--- a/database/event/2574/event_2574_evp_summary.xlsx
+++ b/database/event/2574/event_2574_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.2721</v>
+        <v>9.3474</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0859</v>
+        <v>1.0947</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3244</v>
+        <v>3.2801</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2721</v>
+        <v>9.3474</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3357</v>
+        <v>4.4111</v>
       </c>
       <c r="G2" t="n">
         <v>4.9364</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8832</v>
+        <v>5.1862</v>
       </c>
       <c r="I2" t="n">
-        <v>3.958</v>
+        <v>4.2036</v>
       </c>
       <c r="J2" t="n">
         <v>4.9364</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>8.894400000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -548,7 +548,7 @@
         <v>0.7581</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1937</v>
+        <v>2.1351</v>
       </c>
       <c r="E3" t="n">
         <v>6.4734</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8934</v>
+        <v>6.4204</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6902</v>
+        <v>0.7519</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9594</v>
+        <v>2.114</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8934</v>
+        <v>6.4204</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2624</v>
+        <v>3.7895</v>
       </c>
       <c r="G4" t="n">
         <v>2.631</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2624</v>
+        <v>3.7895</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6443</v>
+        <v>3.0715</v>
       </c>
       <c r="J4" t="n">
         <v>2.631</v>
@@ -621,7 +621,7 @@
         <v>89</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2753</v>
+        <v>5.7025</v>
       </c>
       <c r="N4" t="n">
         <v>183</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9876</v>
+        <v>4.2607</v>
       </c>
       <c r="C5" t="n">
-        <v>0.467</v>
+        <v>0.499</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1895</v>
+        <v>1.2536</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9876</v>
+        <v>4.2607</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2034</v>
+        <v>0.4765</v>
       </c>
       <c r="G5" t="n">
         <v>3.7842</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2034</v>
+        <v>0.4765</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1649</v>
+        <v>0.3862</v>
       </c>
       <c r="J5" t="n">
         <v>3.7842</v>
@@ -667,7 +667,7 @@
         <v>104</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9491</v>
+        <v>4.1704</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -686,7 +686,7 @@
         <v>0.4132</v>
       </c>
       <c r="D6" t="n">
-        <v>1.004</v>
+        <v>0.9618</v>
       </c>
       <c r="E6" t="n">
         <v>3.5283</v>
@@ -732,7 +732,7 @@
         <v>0.391</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9272</v>
+        <v>0.8861</v>
       </c>
       <c r="E7" t="n">
         <v>3.3383</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7828</v>
+        <v>2.7724</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3259</v>
+        <v>0.3247</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7028</v>
+        <v>0.6606</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7828</v>
+        <v>2.7724</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7828</v>
+        <v>2.7724</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7828</v>
+        <v>2.7724</v>
       </c>
       <c r="I8" t="n">
         <v>2.7958</v>
@@ -824,7 +824,7 @@
         <v>0.3213</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6869</v>
+        <v>0.6491</v>
       </c>
       <c r="E9" t="n">
         <v>2.7434</v>
@@ -860,185 +860,185 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0752</v>
+        <v>2.0807</v>
       </c>
       <c r="C10" t="n">
-        <v>0.243</v>
+        <v>0.2437</v>
       </c>
       <c r="D10" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0752</v>
+        <v>2.0807</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.411</v>
+        <v>2.1931</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4862</v>
+        <v>-0.1124</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.411</v>
+        <v>2.1931</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3331</v>
+        <v>1.7776</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4862</v>
+        <v>-0.1124</v>
       </c>
       <c r="K10" t="n">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="L10" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1531</v>
+        <v>1.6652</v>
       </c>
       <c r="N10" t="n">
-        <v>264</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9958</v>
+        <v>2.0752</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2337</v>
+        <v>0.243</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3849</v>
+        <v>0.3828</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9958</v>
+        <v>2.0752</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9958</v>
+        <v>-0.411</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.4862</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9958</v>
+        <v>-0.411</v>
       </c>
       <c r="I11" t="n">
-        <v>2.005</v>
+        <v>-0.3331</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2.4862</v>
       </c>
       <c r="K11" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M11" t="n">
-        <v>2.005</v>
+        <v>2.1531</v>
       </c>
       <c r="N11" t="n">
-        <v>152</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7959</v>
+        <v>1.9883</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2103</v>
+        <v>0.2329</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3041</v>
+        <v>0.3482</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7959</v>
+        <v>1.9883</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9083</v>
+        <v>1.9883</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1124</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9083</v>
+        <v>1.9883</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5468</v>
+        <v>2.005</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1124</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="L12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4344</v>
+        <v>2.005</v>
       </c>
       <c r="N12" t="n">
-        <v>183</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7654</v>
+        <v>1.9775</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2068</v>
+        <v>0.2316</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2918</v>
+        <v>0.3439</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7654</v>
+        <v>1.9775</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4934</v>
+        <v>2.365</v>
       </c>
       <c r="G13" t="n">
-        <v>0.272</v>
+        <v>-0.3875</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4934</v>
+        <v>2.365</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2105</v>
+        <v>1.9169</v>
       </c>
       <c r="J13" t="n">
-        <v>0.272</v>
+        <v>-0.3875</v>
       </c>
       <c r="K13" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="L13" t="n">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4825</v>
+        <v>1.5294</v>
       </c>
       <c r="N13" t="n">
-        <v>183</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7217</v>
+        <v>1.9547</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2016</v>
+        <v>0.2289</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2742</v>
+        <v>0.3348</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7217</v>
+        <v>1.9547</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9421</v>
+        <v>2.1751</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2204</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9421</v>
+        <v>2.1751</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5741</v>
+        <v>1.763</v>
       </c>
       <c r="J14" t="n">
         <v>-0.2204</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3537</v>
+        <v>1.5426</v>
       </c>
       <c r="N14" t="n">
         <v>121</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6583</v>
+        <v>1.7766</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1942</v>
+        <v>0.2081</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2486</v>
+        <v>0.2639</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6583</v>
+        <v>1.7766</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0458</v>
+        <v>1.5046</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3875</v>
+        <v>0.272</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0458</v>
+        <v>1.5046</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6582</v>
+        <v>1.2195</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3875</v>
+        <v>0.272</v>
       </c>
       <c r="K15" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2707</v>
+        <v>1.4915</v>
       </c>
       <c r="N15" t="n">
-        <v>121</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16">
@@ -1146,7 +1146,7 @@
         <v>0.1345</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0426</v>
+        <v>0.0137</v>
       </c>
       <c r="E16" t="n">
         <v>1.1485</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3475</v>
+        <v>0.912</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0407</v>
+        <v>0.1068</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.281</v>
+        <v>-0.0806</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3475</v>
+        <v>0.912</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6604</v>
+        <v>1.912</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3129</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6604</v>
+        <v>1.912</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5353</v>
+        <v>1.5497</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3129</v>
+        <v>-1</v>
       </c>
       <c r="K17" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="L17" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2224</v>
+        <v>0.5497000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3468</v>
+        <v>0.3475</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0406</v>
+        <v>0.0407</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2813</v>
+        <v>-0.3055</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3468</v>
+        <v>0.3475</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3468</v>
+        <v>0.6604</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>-0.3129</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3468</v>
+        <v>0.6604</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0916</v>
+        <v>0.5353</v>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
+        <v>-0.3129</v>
       </c>
       <c r="K18" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0915999999999999</v>
+        <v>0.2224</v>
       </c>
       <c r="N18" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
         <v>0.0395</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.285</v>
+        <v>-0.3094</v>
       </c>
       <c r="E19" t="n">
         <v>0.3376</v>
@@ -1330,7 +1330,7 @@
         <v>0.0192</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3551</v>
+        <v>-0.3786</v>
       </c>
       <c r="E20" t="n">
         <v>0.164</v>
@@ -1376,7 +1376,7 @@
         <v>0.0162</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3654</v>
+        <v>-0.3887</v>
       </c>
       <c r="E21" t="n">
         <v>0.1385</v>
@@ -1422,7 +1422,7 @@
         <v>0.0146</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3709</v>
+        <v>-0.3942</v>
       </c>
       <c r="E22" t="n">
         <v>0.1249</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1644</v>
+        <v>-0.1638</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0193</v>
+        <v>-0.0192</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4878</v>
+        <v>-0.5092</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1644</v>
+        <v>-0.1638</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1644</v>
+        <v>-0.1638</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1644</v>
+        <v>-0.1638</v>
       </c>
       <c r="I23" t="n">
         <v>-0.1652</v>
@@ -1514,7 +1514,7 @@
         <v>-0.0197</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4895</v>
+        <v>-0.5111</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1686</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2204</v>
+        <v>-0.2196</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0258</v>
+        <v>-0.0257</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5104</v>
+        <v>-0.5314</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2204</v>
+        <v>-0.2196</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2204</v>
+        <v>-0.2196</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2204</v>
+        <v>-0.2196</v>
       </c>
       <c r="I25" t="n">
         <v>-0.2214</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0334</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5365</v>
+        <v>-0.5574</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2849</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0378</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5516</v>
+        <v>-0.5724</v>
       </c>
       <c r="E27" t="n">
         <v>-0.3225</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0461</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5804</v>
+        <v>-0.6007</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3936</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0501</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="E29" t="n">
         <v>-0.428</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0561</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.615</v>
+        <v>-0.6349</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4794</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5661</v>
+        <v>-0.5095</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0663</v>
+        <v>-0.0597</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6501</v>
+        <v>-0.6469</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5661</v>
+        <v>-0.5095</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4339</v>
+        <v>0.4905</v>
       </c>
       <c r="G31" t="n">
         <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4339</v>
+        <v>0.4905</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3517</v>
+        <v>0.3976</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>42</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6483</v>
+        <v>-0.6024</v>
       </c>
       <c r="N31" t="n">
         <v>127</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6198</v>
+        <v>-0.6175</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0726</v>
+        <v>-0.0723</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6717</v>
+        <v>-0.6899</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6198</v>
+        <v>-0.6175</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6198</v>
+        <v>-0.6175</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6198</v>
+        <v>-0.6175</v>
       </c>
       <c r="I32" t="n">
         <v>-0.6227</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0771</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6873</v>
+        <v>-0.7062</v>
       </c>
       <c r="E33" t="n">
         <v>-0.6583</v>
@@ -1974,7 +1974,7 @@
         <v>-0.0835</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7094</v>
+        <v>-0.7279</v>
       </c>
       <c r="E34" t="n">
         <v>-0.7129</v>
@@ -2020,7 +2020,7 @@
         <v>-0.0848</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7139</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="E35" t="n">
         <v>-0.7241</v>
@@ -2066,7 +2066,7 @@
         <v>-0.0882</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7255</v>
+        <v>-0.7438</v>
       </c>
       <c r="E36" t="n">
         <v>-0.7528</v>
@@ -2112,7 +2112,7 @@
         <v>-0.0921</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.739</v>
+        <v>-0.7571</v>
       </c>
       <c r="E37" t="n">
         <v>-0.7862</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1411</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9081</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2048</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2027</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1206</v>
+        <v>-1.1335</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7309</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2361</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2357</v>
+        <v>-1.247</v>
       </c>
       <c r="E40" t="n">
         <v>-2.0158</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2333</v>
+        <v>-3.1031</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3787</v>
+        <v>-0.3634</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7275</v>
+        <v>-1.6802</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2333</v>
+        <v>-3.1031</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2333</v>
+        <v>-1.1031</v>
       </c>
       <c r="G41" t="n">
         <v>-2</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2333</v>
+        <v>-1.1031</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9996</v>
+        <v>-0.8941</v>
       </c>
       <c r="J41" t="n">
         <v>-2</v>
@@ -2323,7 +2323,7 @@
         <v>104</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.9996</v>
+        <v>-2.8941</v>
       </c>
       <c r="N41" t="n">
         <v>264</v>

--- a/database/event/2574/event_2574_evp_summary.xlsx
+++ b/database/event/2574/event_2574_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.3474</v>
+        <v>8.3725</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0947</v>
+        <v>0.9805</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2801</v>
+        <v>3.1418</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3474</v>
+        <v>8.3725</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4111</v>
+        <v>4.1825</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9364</v>
+        <v>4.19</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1862</v>
+        <v>9.2502</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2036</v>
+        <v>4.8097</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9364</v>
+        <v>4.19</v>
       </c>
       <c r="K2" t="n">
         <v>160</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>9.140000000000001</v>
+        <v>8.999700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4734</v>
+        <v>6.3138</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7581</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1351</v>
+        <v>2.2124</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4734</v>
+        <v>6.3138</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4501</v>
+        <v>2.7358</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0233</v>
+        <v>3.578</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4501</v>
+        <v>4.1529</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9859</v>
+        <v>2.1593</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0233</v>
+        <v>3.578</v>
       </c>
       <c r="K3" t="n">
         <v>160</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0092</v>
+        <v>5.737299999999999</v>
       </c>
       <c r="N3" t="n">
         <v>264</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4204</v>
+        <v>5.5709</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7519</v>
+        <v>0.6524</v>
       </c>
       <c r="D4" t="n">
-        <v>2.114</v>
+        <v>1.877</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4204</v>
+        <v>5.5709</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7895</v>
+        <v>3.2477</v>
       </c>
       <c r="G4" t="n">
-        <v>2.631</v>
+        <v>2.3232</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7895</v>
+        <v>5.9564</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0715</v>
+        <v>3.0971</v>
       </c>
       <c r="J4" t="n">
-        <v>2.631</v>
+        <v>2.3232</v>
       </c>
       <c r="K4" t="n">
         <v>94</v>
@@ -621,7 +621,7 @@
         <v>89</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7025</v>
+        <v>5.4203</v>
       </c>
       <c r="N4" t="n">
         <v>183</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2607</v>
+        <v>4.5229</v>
       </c>
       <c r="C5" t="n">
-        <v>0.499</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2536</v>
+        <v>1.4038</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2607</v>
+        <v>4.5229</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4765</v>
+        <v>1.0401</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7842</v>
+        <v>3.4828</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4765</v>
+        <v>1.0401</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3862</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7842</v>
+        <v>3.4828</v>
       </c>
       <c r="K5" t="n">
         <v>160</v>
@@ -667,7 +667,7 @@
         <v>104</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1704</v>
+        <v>4.0236</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5283</v>
+        <v>4.1296</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4132</v>
+        <v>0.4836</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9618</v>
+        <v>1.2263</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5283</v>
+        <v>4.1296</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7566</v>
+        <v>2.5836</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7716</v>
+        <v>1.546</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7566</v>
+        <v>3.6167</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4238</v>
+        <v>1.8805</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7716</v>
+        <v>1.546</v>
       </c>
       <c r="K6" t="n">
         <v>94</v>
@@ -713,7 +713,7 @@
         <v>89</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1954</v>
+        <v>3.4265</v>
       </c>
       <c r="N6" t="n">
         <v>183</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3383</v>
+        <v>3.977</v>
       </c>
       <c r="C7" t="n">
-        <v>0.391</v>
+        <v>0.4658</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8861</v>
+        <v>1.1574</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3383</v>
+        <v>3.977</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3383</v>
+        <v>3.977</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3383</v>
+        <v>5.3729</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3383</v>
+        <v>5.3729</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3383</v>
+        <v>5.3729</v>
       </c>
       <c r="N7" t="n">
         <v>149</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7724</v>
+        <v>3.2106</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3247</v>
+        <v>0.376</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6606</v>
+        <v>0.8114</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7724</v>
+        <v>3.2106</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7724</v>
+        <v>3.2106</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7724</v>
+        <v>3.6902</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7958</v>
+        <v>3.842</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7958</v>
+        <v>3.842</v>
       </c>
       <c r="N8" t="n">
         <v>152</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7434</v>
+        <v>2.9289</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3213</v>
+        <v>0.343</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6491</v>
+        <v>0.6842</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7434</v>
+        <v>2.9289</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4544</v>
+        <v>3.1996</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.711</v>
+        <v>-0.2707</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4544</v>
+        <v>5.7872</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7999</v>
+        <v>3.0091</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.711</v>
+        <v>-0.2707</v>
       </c>
       <c r="K9" t="n">
         <v>94</v>
@@ -851,7 +851,7 @@
         <v>89</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0889</v>
+        <v>2.7384</v>
       </c>
       <c r="N9" t="n">
         <v>183</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0807</v>
+        <v>2.9211</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2437</v>
+        <v>0.3421</v>
       </c>
       <c r="D10" t="n">
-        <v>0.385</v>
+        <v>0.6807</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0807</v>
+        <v>2.9211</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1931</v>
+        <v>2.4499</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1124</v>
+        <v>0.4712</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1931</v>
+        <v>3.1455</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7776</v>
+        <v>1.6355</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1124</v>
+        <v>0.4712</v>
       </c>
       <c r="K10" t="n">
         <v>94</v>
@@ -897,7 +897,7 @@
         <v>89</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6652</v>
+        <v>2.1067</v>
       </c>
       <c r="N10" t="n">
         <v>183</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0752</v>
+        <v>2.7291</v>
       </c>
       <c r="C11" t="n">
-        <v>0.243</v>
+        <v>0.3196</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3828</v>
+        <v>0.594</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0752</v>
+        <v>2.7291</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.411</v>
+        <v>2.6595</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4862</v>
+        <v>0.0696</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.411</v>
+        <v>3.884</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3331</v>
+        <v>2.0195</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4862</v>
+        <v>0.0696</v>
       </c>
       <c r="K11" t="n">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="L11" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1531</v>
+        <v>2.0891</v>
       </c>
       <c r="N11" t="n">
-        <v>264</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9883</v>
+        <v>2.4829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2329</v>
+        <v>0.2908</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3482</v>
+        <v>0.4829</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9883</v>
+        <v>2.4829</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9883</v>
+        <v>2.5088</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.0259</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9883</v>
+        <v>3.353</v>
       </c>
       <c r="I12" t="n">
-        <v>2.005</v>
+        <v>1.7434</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.0259</v>
       </c>
       <c r="K12" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M12" t="n">
-        <v>2.005</v>
+        <v>1.7175</v>
       </c>
       <c r="N12" t="n">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9775</v>
+        <v>2.4288</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2316</v>
+        <v>0.2845</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3439</v>
+        <v>0.4585</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9775</v>
+        <v>2.4288</v>
       </c>
       <c r="F13" t="n">
-        <v>2.365</v>
+        <v>2.5899</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3875</v>
+        <v>-0.1611</v>
       </c>
       <c r="H13" t="n">
-        <v>2.365</v>
+        <v>3.6388</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9169</v>
+        <v>1.892</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3875</v>
+        <v>-0.1611</v>
       </c>
       <c r="K13" t="n">
         <v>64</v>
@@ -1035,7 +1035,7 @@
         <v>57</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5294</v>
+        <v>1.7309</v>
       </c>
       <c r="N13" t="n">
         <v>121</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9547</v>
+        <v>2.2145</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2289</v>
+        <v>0.2594</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3348</v>
+        <v>0.3617</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9547</v>
+        <v>2.2145</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1751</v>
+        <v>-0.3639</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2204</v>
+        <v>2.5784</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1751</v>
+        <v>-0.3639</v>
       </c>
       <c r="I14" t="n">
-        <v>1.763</v>
+        <v>-0.1892</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2204</v>
+        <v>2.5784</v>
       </c>
       <c r="K14" t="n">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="L14" t="n">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5426</v>
+        <v>2.3892</v>
       </c>
       <c r="N14" t="n">
-        <v>121</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7766</v>
+        <v>2.181</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2081</v>
+        <v>0.2554</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2639</v>
+        <v>0.3466</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7766</v>
+        <v>2.181</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5046</v>
+        <v>2.181</v>
       </c>
       <c r="G15" t="n">
-        <v>0.272</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5046</v>
+        <v>2.181</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2195</v>
+        <v>2.2707</v>
       </c>
       <c r="J15" t="n">
-        <v>0.272</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="L15" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4915</v>
+        <v>2.2707</v>
       </c>
       <c r="N15" t="n">
-        <v>183</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>keev</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1485</v>
+        <v>1.5803</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1345</v>
+        <v>0.1851</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0137</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1485</v>
+        <v>1.5803</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1485</v>
+        <v>2.3334</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.7531</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1485</v>
+        <v>2.7353</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1485</v>
+        <v>1.4222</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.7531</v>
       </c>
       <c r="K16" t="n">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1485</v>
+        <v>0.6690999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>keev</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.912</v>
+        <v>1.3765</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1068</v>
+        <v>0.1612</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0806</v>
+        <v>-0.0166</v>
       </c>
       <c r="E17" t="n">
-        <v>0.912</v>
+        <v>1.3765</v>
       </c>
       <c r="F17" t="n">
-        <v>1.912</v>
+        <v>1.3765</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.912</v>
+        <v>1.3765</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5497</v>
+        <v>1.3765</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5497000000000001</v>
+        <v>1.3765</v>
       </c>
       <c r="N17" t="n">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3475</v>
+        <v>1.0465</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0407</v>
+        <v>0.1226</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3055</v>
+        <v>-0.1656</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3475</v>
+        <v>1.0465</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6604</v>
+        <v>1.1957</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3129</v>
+        <v>-0.1492</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6604</v>
+        <v>1.1957</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5353</v>
+        <v>0.6217</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3129</v>
+        <v>-0.1492</v>
       </c>
       <c r="K18" t="n">
         <v>64</v>
@@ -1265,7 +1265,7 @@
         <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2224</v>
+        <v>0.4725</v>
       </c>
       <c r="N18" t="n">
         <v>121</v>
@@ -1274,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>vSa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3376</v>
+        <v>0.4998</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0395</v>
+        <v>0.0585</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3094</v>
+        <v>-0.4124</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3376</v>
+        <v>0.4998</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3376</v>
+        <v>0.4998</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3376</v>
+        <v>0.4998</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3376</v>
+        <v>0.4998</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3376</v>
+        <v>0.4998</v>
       </c>
       <c r="N19" t="n">
-        <v>149</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.164</v>
+        <v>0.4408</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0192</v>
+        <v>0.0516</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3786</v>
+        <v>-0.439</v>
       </c>
       <c r="E20" t="n">
-        <v>0.164</v>
+        <v>0.4408</v>
       </c>
       <c r="F20" t="n">
-        <v>0.164</v>
+        <v>1.4022</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.9614</v>
       </c>
       <c r="H20" t="n">
-        <v>0.164</v>
+        <v>1.4022</v>
       </c>
       <c r="I20" t="n">
-        <v>0.164</v>
+        <v>0.7291</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.9614</v>
       </c>
       <c r="K20" t="n">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>0.164</v>
+        <v>-0.2323000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1385</v>
+        <v>0.4369</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0162</v>
+        <v>0.0512</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3887</v>
+        <v>-0.4408</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1385</v>
+        <v>0.4369</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1385</v>
+        <v>0.4369</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1385</v>
+        <v>0.4369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1385</v>
+        <v>0.4369</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1385</v>
+        <v>0.4369</v>
       </c>
       <c r="N21" t="n">
-        <v>91</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vSa</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1249</v>
+        <v>0.3978</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0146</v>
+        <v>0.0466</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3942</v>
+        <v>-0.4584</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1249</v>
+        <v>0.3978</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1249</v>
+        <v>0.3978</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1249</v>
+        <v>0.3978</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1249</v>
+        <v>0.3978</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1249</v>
+        <v>0.3978</v>
       </c>
       <c r="N22" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1638</v>
+        <v>0.2954</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0192</v>
+        <v>0.0346</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5092</v>
+        <v>-0.5047</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1638</v>
+        <v>0.2954</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1638</v>
+        <v>0.2954</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1638</v>
+        <v>0.2954</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1652</v>
+        <v>0.3076</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1652</v>
+        <v>0.3076</v>
       </c>
       <c r="N23" t="n">
         <v>152</v>
@@ -1504,35 +1504,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1686</v>
+        <v>0.2488</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0197</v>
+        <v>0.0291</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5111</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1686</v>
+        <v>0.2488</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8314</v>
+        <v>1.0303</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>-0.7815</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8314</v>
+        <v>1.0303</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.5357</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>-0.7815</v>
       </c>
       <c r="K24" t="n">
         <v>85</v>
@@ -1541,7 +1541,7 @@
         <v>42</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3260999999999999</v>
+        <v>-0.2458</v>
       </c>
       <c r="N24" t="n">
         <v>127</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2196</v>
+        <v>0.1754</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0257</v>
+        <v>0.0205</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5314</v>
+        <v>-0.5588</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2196</v>
+        <v>0.1754</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2196</v>
+        <v>0.1754</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2196</v>
+        <v>0.1754</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2214</v>
+        <v>0.1754</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2214</v>
+        <v>0.1754</v>
       </c>
       <c r="N25" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2849</v>
+        <v>0.095</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0334</v>
+        <v>0.0111</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5574</v>
+        <v>-0.5951</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2849</v>
+        <v>0.095</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2849</v>
+        <v>0.095</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2849</v>
+        <v>0.095</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2849</v>
+        <v>0.0989</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2849</v>
+        <v>0.0989</v>
       </c>
       <c r="N26" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3225</v>
+        <v>0.0574</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0378</v>
+        <v>0.0067</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5724</v>
+        <v>-0.6121</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3225</v>
+        <v>0.0574</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3225</v>
+        <v>0.0574</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3225</v>
+        <v>0.0574</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3225</v>
+        <v>0.0574</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3225</v>
+        <v>0.0574</v>
       </c>
       <c r="N27" t="n">
         <v>91</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3936</v>
+        <v>-0.0072</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0461</v>
+        <v>-0.0008</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6007</v>
+        <v>-0.6413</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3936</v>
+        <v>-0.0072</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.3173</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>-0.3245</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.3173</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4915</v>
+        <v>0.165</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>-0.3245</v>
       </c>
       <c r="K28" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.5085</v>
+        <v>-0.1595</v>
       </c>
       <c r="N28" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.428</v>
+        <v>-0.0256</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0501</v>
+        <v>-0.003</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.6496</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.428</v>
+        <v>-0.0256</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0605</v>
+        <v>0.8612</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4885</v>
+        <v>-0.8868</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0605</v>
+        <v>0.8612</v>
       </c>
       <c r="I29" t="n">
-        <v>0.049</v>
+        <v>0.4478</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4885</v>
+        <v>-0.8868</v>
       </c>
       <c r="K29" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="L29" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4395</v>
+        <v>-0.4390000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4794</v>
+        <v>-0.1337</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0561</v>
+        <v>-0.0157</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6349</v>
+        <v>-0.6984</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4794</v>
+        <v>-0.1337</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4794</v>
+        <v>-0.1337</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4794</v>
+        <v>-0.1337</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4794</v>
+        <v>-0.1337</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4794</v>
+        <v>-0.1337</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5095</v>
+        <v>-0.1789</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0597</v>
+        <v>-0.021</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6469</v>
+        <v>-0.7188</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5095</v>
+        <v>-0.1789</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4905</v>
+        <v>-0.1789</v>
       </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4905</v>
+        <v>-0.1789</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3976</v>
+        <v>-0.1789</v>
       </c>
       <c r="J31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L31" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6024</v>
+        <v>-0.1789</v>
       </c>
       <c r="N31" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6175</v>
+        <v>-0.2593</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0723</v>
+        <v>-0.0304</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6899</v>
+        <v>-0.7551</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6175</v>
+        <v>-0.2593</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6175</v>
+        <v>-0.2593</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6175</v>
+        <v>-0.2593</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6227</v>
+        <v>-0.27</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6227</v>
+        <v>-0.27</v>
       </c>
       <c r="N32" t="n">
         <v>152</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6583</v>
+        <v>-0.3016</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0771</v>
+        <v>-0.0353</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7062</v>
+        <v>-0.7742</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6583</v>
+        <v>-0.3016</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6583</v>
+        <v>-0.3016</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6583</v>
+        <v>-0.3016</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6583</v>
+        <v>-0.3016</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6583</v>
+        <v>-0.3016</v>
       </c>
       <c r="N33" t="n">
         <v>77</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>moose</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7129</v>
+        <v>-0.4666</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0835</v>
+        <v>-0.0546</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7279</v>
+        <v>-0.8487</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7129</v>
+        <v>-0.4666</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7129</v>
+        <v>-0.4666</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7129</v>
+        <v>-0.4666</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7129</v>
+        <v>-0.4666</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7129</v>
+        <v>-0.4666</v>
       </c>
       <c r="N34" t="n">
         <v>77</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>moose</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7241</v>
+        <v>-0.4936</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0848</v>
+        <v>-0.0578</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.8609</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7241</v>
+        <v>-0.4936</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7241</v>
+        <v>-0.4936</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7241</v>
+        <v>-0.4936</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7241</v>
+        <v>-0.4936</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7241</v>
+        <v>-0.4936</v>
       </c>
       <c r="N35" t="n">
         <v>77</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>dazzLe</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7528</v>
+        <v>-0.83</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0882</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7438</v>
+        <v>-1.0127</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7528</v>
+        <v>-0.83</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9796</v>
+        <v>-0.83</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9796</v>
+        <v>-0.83</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.794</v>
+        <v>-0.83</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="L36" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5672</v>
+        <v>-0.83</v>
       </c>
       <c r="N36" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7862</v>
+        <v>-0.8928</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0921</v>
+        <v>-0.1046</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7571</v>
+        <v>-1.0411</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7862</v>
+        <v>-0.8928</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8733</v>
+        <v>-1.0964</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0871</v>
+        <v>0.2036</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8733</v>
+        <v>-1.0964</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7078</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0871</v>
+        <v>0.2036</v>
       </c>
       <c r="K37" t="n">
         <v>85</v>
@@ -2139,7 +2139,7 @@
         <v>42</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6207</v>
+        <v>-0.3665</v>
       </c>
       <c r="N37" t="n">
         <v>127</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dazzLe</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2048</v>
+        <v>-1.0011</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1411</v>
+        <v>-0.1172</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-1.09</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2048</v>
+        <v>-1.0011</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2048</v>
+        <v>-1.3242</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.3231</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2048</v>
+        <v>-1.3242</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2048</v>
+        <v>-0.6885</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.3231</v>
       </c>
       <c r="K38" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2048</v>
+        <v>-0.3654</v>
       </c>
       <c r="N38" t="n">
-        <v>77</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7309</v>
+        <v>-1.1944</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2027</v>
+        <v>-0.1399</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1335</v>
+        <v>-1.1772</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7309</v>
+        <v>-1.1944</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7309</v>
+        <v>-1.1944</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7309</v>
+        <v>-1.1944</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7309</v>
+        <v>-1.1944</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7309</v>
+        <v>-1.1944</v>
       </c>
       <c r="N39" t="n">
         <v>91</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0158</v>
+        <v>-1.3902</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2361</v>
+        <v>-0.1628</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.247</v>
+        <v>-1.2656</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0158</v>
+        <v>-1.3902</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0158</v>
+        <v>-1.3902</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0158</v>
+        <v>-1.3902</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0158</v>
+        <v>-1.3902</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0158</v>
+        <v>-1.3902</v>
       </c>
       <c r="N40" t="n">
         <v>149</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.1031</v>
+        <v>-2.9801</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3634</v>
+        <v>-0.349</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6802</v>
+        <v>-1.9834</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.1031</v>
+        <v>-2.9801</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1031</v>
+        <v>-0.9801</v>
       </c>
       <c r="G41" t="n">
         <v>-2</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1031</v>
+        <v>-0.9801</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8941</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="J41" t="n">
         <v>-2</v>
@@ -2323,7 +2323,7 @@
         <v>104</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8941</v>
+        <v>-2.5096</v>
       </c>
       <c r="N41" t="n">
         <v>264</v>
@@ -2429,10 +2429,10 @@
         <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1299</v>
+        <v>1.8608</v>
       </c>
       <c r="J2" t="n">
-        <v>42.598</v>
+        <v>37.216</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.278</v>
+        <v>1.2096</v>
       </c>
       <c r="J3" t="n">
-        <v>25.56</v>
+        <v>24.192</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.48</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0048</v>
+        <v>1.0709</v>
       </c>
       <c r="J4" t="n">
-        <v>20.096</v>
+        <v>21.418</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.39</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8069</v>
+        <v>0.9329</v>
       </c>
       <c r="J5" t="n">
-        <v>16.138</v>
+        <v>18.658</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6686</v>
+        <v>-0.6049</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.372</v>
+        <v>-12.098</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1434</v>
+        <v>-0.1377</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.868</v>
+        <v>-2.754</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.83</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1758</v>
+        <v>-0.1602</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.516</v>
+        <v>-3.204</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.65</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4839</v>
+        <v>-0.3384</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.678000000000001</v>
+        <v>-6.768</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.52</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6766</v>
+        <v>-0.459</v>
       </c>
       <c r="J10" t="n">
-        <v>-13.532</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7034</v>
+        <v>-0.4777</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.068</v>
+        <v>-9.554</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.72</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5968</v>
+        <v>1.3905</v>
       </c>
       <c r="J12" t="n">
-        <v>43.1136</v>
+        <v>37.5435</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2375</v>
+        <v>1.1587</v>
       </c>
       <c r="J13" t="n">
-        <v>33.4125</v>
+        <v>31.2849</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.26</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6118</v>
+        <v>0.6854</v>
       </c>
       <c r="J14" t="n">
-        <v>16.5186</v>
+        <v>18.5058</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3058</v>
+        <v>0.3905</v>
       </c>
       <c r="J15" t="n">
-        <v>8.256600000000001</v>
+        <v>10.5435</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7269</v>
+        <v>-0.67</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.6263</v>
+        <v>-18.09</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2678</v>
+        <v>0.2715</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2306</v>
+        <v>7.3305</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.92</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0707</v>
+        <v>-0.081</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9089</v>
+        <v>-2.187</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5159</v>
+        <v>-0.3437</v>
       </c>
       <c r="J19" t="n">
-        <v>-13.9293</v>
+        <v>-9.2799</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.599</v>
+        <v>-0.4</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.173</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6123</v>
+        <v>-0.4093</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.5321</v>
+        <v>-11.0511</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.83</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2331</v>
+        <v>-0.1841</v>
       </c>
       <c r="J22" t="n">
-        <v>-5.8275</v>
+        <v>-4.6025</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2331</v>
+        <v>-0.1841</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.8275</v>
+        <v>-4.6025</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3495</v>
+        <v>-0.2418</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.737500000000001</v>
+        <v>-6.045</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3846</v>
+        <v>-0.2606</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.615</v>
+        <v>-6.515</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.73</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.417</v>
+        <v>-0.2795</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.425</v>
+        <v>-6.9875</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.76</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6687</v>
+        <v>1.1664</v>
       </c>
       <c r="J27" t="n">
-        <v>41.7175</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9263</v>
+        <v>0.6969</v>
       </c>
       <c r="J28" t="n">
-        <v>23.1575</v>
+        <v>17.4225</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3864</v>
+        <v>0.414</v>
       </c>
       <c r="J29" t="n">
-        <v>9.66</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.06</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0829</v>
+        <v>0.1634</v>
       </c>
       <c r="J30" t="n">
-        <v>2.0725</v>
+        <v>4.085</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.06</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0829</v>
+        <v>0.1634</v>
       </c>
       <c r="J31" t="n">
-        <v>2.0725</v>
+        <v>4.085</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3202</v>
+        <v>0.3877</v>
       </c>
       <c r="J32" t="n">
-        <v>5.4434</v>
+        <v>6.5909</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.42</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.5113</v>
       </c>
       <c r="J33" t="n">
-        <v>-12.3641</v>
+        <v>-8.6921</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.41</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7437</v>
+        <v>-0.5209</v>
       </c>
       <c r="J34" t="n">
-        <v>-12.6429</v>
+        <v>-8.8553</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.25</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9742</v>
+        <v>-0.6819</v>
       </c>
       <c r="J35" t="n">
-        <v>-16.5614</v>
+        <v>-11.5923</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.23</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0007</v>
+        <v>-0.7027</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.0119</v>
+        <v>-11.9459</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.57</v>
       </c>
       <c r="I37" t="n">
-        <v>2.3202</v>
+        <v>1.9551</v>
       </c>
       <c r="J37" t="n">
-        <v>39.4434</v>
+        <v>33.2367</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>2.26</v>
       </c>
       <c r="I38" t="n">
-        <v>2.0654</v>
+        <v>1.6334</v>
       </c>
       <c r="J38" t="n">
-        <v>35.1118</v>
+        <v>27.7678</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5386</v>
       </c>
       <c r="J39" t="n">
-        <v>9.263299999999999</v>
+        <v>9.1562</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.14</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2061</v>
+        <v>0.3136</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5037</v>
+        <v>5.3312</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.08</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0512</v>
+        <v>0.1474</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8704</v>
+        <v>2.5058</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2871</v>
+        <v>0.3028</v>
       </c>
       <c r="J42" t="n">
-        <v>7.7517</v>
+        <v>8.175599999999999</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1812</v>
+        <v>0.17</v>
       </c>
       <c r="J43" t="n">
-        <v>4.8924</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1672</v>
+        <v>-0.1235</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.5144</v>
+        <v>-3.3345</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3669</v>
+        <v>-0.2353</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.9063</v>
+        <v>-6.3531</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6398</v>
+        <v>-0.4258</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.2746</v>
+        <v>-11.4966</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5005</v>
+        <v>1.052</v>
       </c>
       <c r="J47" t="n">
-        <v>40.5135</v>
+        <v>28.404</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.29</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7277</v>
+        <v>0.5829</v>
       </c>
       <c r="J48" t="n">
-        <v>19.6479</v>
+        <v>15.7383</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.21</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5016</v>
+        <v>0.4753</v>
       </c>
       <c r="J49" t="n">
-        <v>13.5432</v>
+        <v>12.8331</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.19</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4497</v>
+        <v>0.4465</v>
       </c>
       <c r="J50" t="n">
-        <v>12.1419</v>
+        <v>12.0555</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.96</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.315</v>
+        <v>-0.2322</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.505000000000001</v>
+        <v>-6.2694</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.34</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5937</v>
+        <v>0.5584</v>
       </c>
       <c r="J52" t="n">
-        <v>17.811</v>
+        <v>16.752</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2523</v>
+        <v>0.2647</v>
       </c>
       <c r="J53" t="n">
-        <v>7.569</v>
+        <v>7.941</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3213</v>
+        <v>-0.201</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.638999999999999</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.71</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4941</v>
+        <v>-0.3192</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.823</v>
+        <v>-9.576000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5075</v>
+        <v>-0.3287</v>
       </c>
       <c r="J56" t="n">
-        <v>-15.225</v>
+        <v>-9.861000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.52</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2532</v>
+        <v>0.8888</v>
       </c>
       <c r="J57" t="n">
-        <v>37.596</v>
+        <v>26.664</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.4</v>
       </c>
       <c r="I58" t="n">
-        <v>1.0062</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>30.186</v>
+        <v>22.032</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.28</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7329</v>
+        <v>0.5749</v>
       </c>
       <c r="J59" t="n">
-        <v>21.987</v>
+        <v>17.247</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3398</v>
+        <v>0.3772</v>
       </c>
       <c r="J60" t="n">
-        <v>10.194</v>
+        <v>11.316</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8491</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-25.473</v>
+        <v>-24.177</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.51</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1995</v>
+        <v>1.1348</v>
       </c>
       <c r="J62" t="n">
-        <v>29.9875</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7325</v>
+        <v>0.7743</v>
       </c>
       <c r="J63" t="n">
-        <v>18.3125</v>
+        <v>19.3575</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.29</v>
       </c>
       <c r="I64" t="n">
-        <v>0.703</v>
+        <v>0.7526</v>
       </c>
       <c r="J64" t="n">
-        <v>17.575</v>
+        <v>18.815</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5632</v>
+        <v>0.6399</v>
       </c>
       <c r="J65" t="n">
-        <v>14.08</v>
+        <v>15.9975</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.199</v>
+        <v>0.2818</v>
       </c>
       <c r="J66" t="n">
-        <v>4.975</v>
+        <v>7.045</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3156</v>
+        <v>0.3355</v>
       </c>
       <c r="J67" t="n">
-        <v>7.89</v>
+        <v>8.387499999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1698</v>
+        <v>0.148</v>
       </c>
       <c r="J68" t="n">
-        <v>4.245</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0881</v>
+        <v>0.05</v>
       </c>
       <c r="J69" t="n">
-        <v>2.2025</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5854</v>
+        <v>-0.3883</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.635</v>
+        <v>-9.7075</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.32</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9473</v>
+        <v>-0.6629</v>
       </c>
       <c r="J71" t="n">
-        <v>-23.6825</v>
+        <v>-16.5725</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.95</v>
       </c>
       <c r="I72" t="n">
-        <v>1.9247</v>
+        <v>1.6245</v>
       </c>
       <c r="J72" t="n">
-        <v>36.5693</v>
+        <v>30.8655</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.49</v>
       </c>
       <c r="I73" t="n">
-        <v>1.089</v>
+        <v>1.0888</v>
       </c>
       <c r="J73" t="n">
-        <v>20.691</v>
+        <v>20.6872</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.36</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7745</v>
+        <v>0.8834</v>
       </c>
       <c r="J74" t="n">
-        <v>14.7155</v>
+        <v>16.7846</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.18</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3599</v>
+        <v>0.4645</v>
       </c>
       <c r="J75" t="n">
-        <v>6.8381</v>
+        <v>8.8255</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.15</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2861</v>
+        <v>0.3873</v>
       </c>
       <c r="J76" t="n">
-        <v>5.4359</v>
+        <v>7.3587</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.37</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7076</v>
+        <v>0.8954</v>
       </c>
       <c r="J77" t="n">
-        <v>13.4444</v>
+        <v>17.0126</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0255</v>
+        <v>-0.0514</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.4845</v>
+        <v>-0.9766</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.52</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.6989</v>
+        <v>-0.4719</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.2791</v>
+        <v>-8.966100000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7493</v>
+        <v>-0.509</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.2367</v>
+        <v>-9.670999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.44</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7984</v>
+        <v>-0.546</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.1696</v>
+        <v>-10.374</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5668</v>
+        <v>1.3702</v>
       </c>
       <c r="J82" t="n">
-        <v>32.9028</v>
+        <v>28.7742</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.48</v>
       </c>
       <c r="I83" t="n">
-        <v>1.1435</v>
+        <v>1.0991</v>
       </c>
       <c r="J83" t="n">
-        <v>24.0135</v>
+        <v>23.0811</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.37</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9083</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>19.0743</v>
+        <v>19.5069</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4128</v>
+        <v>-0.3328</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.668799999999999</v>
+        <v>-6.9888</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.91</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4699</v>
+        <v>-0.393</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.867900000000001</v>
+        <v>-8.253</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5436</v>
+        <v>0.6519</v>
       </c>
       <c r="J87" t="n">
-        <v>11.4156</v>
+        <v>13.6899</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.79</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2929</v>
+        <v>-0.2217</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.1509</v>
+        <v>-4.6557</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5435</v>
+        <v>-0.3622</v>
       </c>
       <c r="J89" t="n">
-        <v>-11.4135</v>
+        <v>-7.6062</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5435</v>
+        <v>-0.3622</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.4135</v>
+        <v>-7.6062</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.4835</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.0192</v>
+        <v>-10.1535</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.5654</v>
       </c>
       <c r="J92" t="n">
-        <v>15.26</v>
+        <v>14.135</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2463</v>
+        <v>0.2048</v>
       </c>
       <c r="J93" t="n">
-        <v>6.1575</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.9</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2266</v>
+        <v>-0.1338</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.665</v>
+        <v>-3.345</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.82</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3534</v>
+        <v>-0.2184</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.835000000000001</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4112</v>
+        <v>-0.2584</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.28</v>
+        <v>-6.46</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6349</v>
+        <v>0.5542</v>
       </c>
       <c r="J97" t="n">
-        <v>15.8725</v>
+        <v>13.855</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5104</v>
+        <v>0.4378</v>
       </c>
       <c r="J98" t="n">
-        <v>12.76</v>
+        <v>10.945</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4306</v>
+        <v>0.3658</v>
       </c>
       <c r="J99" t="n">
-        <v>10.765</v>
+        <v>9.145</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1694</v>
+        <v>-0.0873</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.235</v>
+        <v>-2.1825</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.4396</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.495</v>
+        <v>-10.99</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.55</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3934</v>
+        <v>1.2494</v>
       </c>
       <c r="J102" t="n">
-        <v>39.0152</v>
+        <v>34.9832</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.21</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6564</v>
+        <v>0.622</v>
       </c>
       <c r="J103" t="n">
-        <v>18.3792</v>
+        <v>17.416</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.95</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2714</v>
+        <v>-0.2133</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.5992</v>
+        <v>-5.9724</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.64</v>
+        <v>-0.5863</v>
       </c>
       <c r="J105" t="n">
-        <v>-17.92</v>
+        <v>-16.4164</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.762</v>
+        <v>-0.7159</v>
       </c>
       <c r="J106" t="n">
-        <v>-21.336</v>
+        <v>-20.0452</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4372</v>
+        <v>0.5085</v>
       </c>
       <c r="J107" t="n">
-        <v>12.2416</v>
+        <v>14.238</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.11</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2417</v>
+        <v>0.2646</v>
       </c>
       <c r="J108" t="n">
-        <v>6.7676</v>
+        <v>7.4088</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>0.034</v>
+        <v>0.0368</v>
       </c>
       <c r="J109" t="n">
-        <v>0.952</v>
+        <v>1.0304</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.87</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2798</v>
+        <v>-0.1678</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.8344</v>
+        <v>-4.6984</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.371</v>
+        <v>-0.2299</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.388</v>
+        <v>-6.4372</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.8</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2696</v>
+        <v>-0.2105</v>
       </c>
       <c r="J112" t="n">
-        <v>-5.9312</v>
+        <v>-4.631</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.79</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2866</v>
+        <v>-0.2204</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.3052</v>
+        <v>-4.8488</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3041</v>
+        <v>-0.2301</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.6902</v>
+        <v>-5.0622</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.77</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3221</v>
+        <v>-0.2396</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.0862</v>
+        <v>-5.2712</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.64</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5401</v>
+        <v>-0.3607</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.8822</v>
+        <v>-7.9354</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.7295</v>
+        <v>1.4852</v>
       </c>
       <c r="J117" t="n">
-        <v>38.049</v>
+        <v>32.6744</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.6057</v>
+        <v>1.4048</v>
       </c>
       <c r="J118" t="n">
-        <v>35.3254</v>
+        <v>30.9056</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.66</v>
       </c>
       <c r="I119" t="n">
-        <v>1.4222</v>
+        <v>1.2886</v>
       </c>
       <c r="J119" t="n">
-        <v>31.2884</v>
+        <v>28.3492</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.12</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2062</v>
+        <v>0.3043</v>
       </c>
       <c r="J120" t="n">
-        <v>4.5364</v>
+        <v>6.6946</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7301</v>
+        <v>-0.6728</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.0622</v>
+        <v>-14.8016</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6669</v>
+        <v>0.5875</v>
       </c>
       <c r="J122" t="n">
-        <v>16.0056</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.36</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5453</v>
+        <v>0.4744</v>
       </c>
       <c r="J123" t="n">
-        <v>13.0872</v>
+        <v>11.3856</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2923</v>
+        <v>0.2604</v>
       </c>
       <c r="J124" t="n">
-        <v>7.0152</v>
+        <v>6.2496</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.11</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1647</v>
+        <v>0.1705</v>
       </c>
       <c r="J125" t="n">
-        <v>3.9528</v>
+        <v>4.092</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5446</v>
+        <v>-0.3525</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.0704</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.53</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8048</v>
+        <v>0.775</v>
       </c>
       <c r="J127" t="n">
-        <v>19.3152</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1441</v>
+        <v>0.1099</v>
       </c>
       <c r="J128" t="n">
-        <v>3.4584</v>
+        <v>2.6376</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3035</v>
+        <v>-0.1856</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.284</v>
+        <v>-4.4544</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3343</v>
+        <v>-0.2063</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.023199999999999</v>
+        <v>-4.9512</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5934</v>
+        <v>-0.3902</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.2416</v>
+        <v>-9.364800000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.17</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3691</v>
+        <v>0.4115</v>
       </c>
       <c r="J132" t="n">
-        <v>8.4893</v>
+        <v>9.464499999999999</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1493</v>
+        <v>0.1361</v>
       </c>
       <c r="J133" t="n">
-        <v>3.4339</v>
+        <v>3.1303</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0549</v>
       </c>
       <c r="J134" t="n">
-        <v>1.8446</v>
+        <v>1.2627</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.194</v>
+        <v>-0.1256</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.462</v>
+        <v>-2.8888</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.47</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7886</v>
+        <v>-0.5383</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.1378</v>
+        <v>-12.3809</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5228</v>
+        <v>1.3401</v>
       </c>
       <c r="J137" t="n">
-        <v>35.0244</v>
+        <v>30.8223</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.38</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9438</v>
+        <v>0.9549</v>
       </c>
       <c r="J138" t="n">
-        <v>21.7074</v>
+        <v>21.9627</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.24</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5875</v>
+        <v>0.6458</v>
       </c>
       <c r="J139" t="n">
-        <v>13.5125</v>
+        <v>14.8534</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.04</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0296</v>
+        <v>0.106</v>
       </c>
       <c r="J140" t="n">
-        <v>0.6808</v>
+        <v>2.438</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3763</v>
+        <v>-0.2959</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.6549</v>
+        <v>-6.8057</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7672</v>
+        <v>0.9548</v>
       </c>
       <c r="J142" t="n">
-        <v>23.016</v>
+        <v>28.644</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0094</v>
+        <v>0.0011</v>
       </c>
       <c r="J143" t="n">
-        <v>0.282</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3063</v>
+        <v>-0.1868</v>
       </c>
       <c r="J144" t="n">
-        <v>-9.189</v>
+        <v>-5.604</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.83</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3369</v>
+        <v>-0.2075</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.107</v>
+        <v>-6.225</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4239</v>
+        <v>-0.2676</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.717</v>
+        <v>-8.028</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>1.088</v>
+        <v>1.0483</v>
       </c>
       <c r="J147" t="n">
-        <v>32.64</v>
+        <v>31.449</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.2</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5825</v>
       </c>
       <c r="J148" t="n">
-        <v>18.159</v>
+        <v>17.475</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.532</v>
       </c>
       <c r="J149" t="n">
-        <v>16.587</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.98</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1834</v>
+        <v>-0.1193</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.502</v>
+        <v>-3.579</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.844</v>
+        <v>-0.8028</v>
       </c>
       <c r="J151" t="n">
-        <v>-25.32</v>
+        <v>-24.084</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2307</v>
+        <v>-0.2034</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.8447</v>
+        <v>-4.2714</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.59</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.5319</v>
+        <v>-0.3817</v>
       </c>
       <c r="J153" t="n">
-        <v>-11.1699</v>
+        <v>-8.015700000000001</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.57</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5688</v>
+        <v>-0.3994</v>
       </c>
       <c r="J154" t="n">
-        <v>-11.9448</v>
+        <v>-8.3874</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5855</v>
+        <v>-0.4085</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.2955</v>
+        <v>-8.5785</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.49</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.4736</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.511</v>
+        <v>-9.945600000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.85</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7481</v>
+        <v>1.4998</v>
       </c>
       <c r="J157" t="n">
-        <v>36.7101</v>
+        <v>31.4958</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4046</v>
+        <v>1.2822</v>
       </c>
       <c r="J158" t="n">
-        <v>29.4966</v>
+        <v>26.9262</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I159" t="n">
-        <v>0.7728</v>
+        <v>0.8954</v>
       </c>
       <c r="J159" t="n">
-        <v>16.2288</v>
+        <v>18.8034</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.26</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5302</v>
+        <v>0.6482</v>
       </c>
       <c r="J160" t="n">
-        <v>11.1342</v>
+        <v>13.6122</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.25</v>
       </c>
       <c r="I161" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.6246</v>
       </c>
       <c r="J161" t="n">
-        <v>10.6596</v>
+        <v>13.1166</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.511</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="J162" t="n">
-        <v>14.308</v>
+        <v>16.8084</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.85</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2649</v>
+        <v>-0.1739</v>
       </c>
       <c r="J163" t="n">
-        <v>-7.4172</v>
+        <v>-4.8692</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.77</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3937</v>
+        <v>-0.2537</v>
       </c>
       <c r="J164" t="n">
-        <v>-11.0236</v>
+        <v>-7.1036</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3937</v>
+        <v>-0.2537</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.0236</v>
+        <v>-7.1036</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4376</v>
+        <v>-0.2829</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.2528</v>
+        <v>-7.9212</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8763</v>
+        <v>0.8807</v>
       </c>
       <c r="J167" t="n">
-        <v>24.5364</v>
+        <v>24.6596</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.34</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8763</v>
+        <v>0.8807</v>
       </c>
       <c r="J168" t="n">
-        <v>24.5364</v>
+        <v>24.6596</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4801</v>
+        <v>0.5344</v>
       </c>
       <c r="J169" t="n">
-        <v>13.4428</v>
+        <v>14.9632</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.14</v>
       </c>
       <c r="I170" t="n">
-        <v>0.342</v>
+        <v>0.4081</v>
       </c>
       <c r="J170" t="n">
-        <v>9.576000000000001</v>
+        <v>11.4268</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1097</v>
+        <v>0.1807</v>
       </c>
       <c r="J171" t="n">
-        <v>3.0716</v>
+        <v>5.0596</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7745</v>
+        <v>0.7442</v>
       </c>
       <c r="J172" t="n">
-        <v>45.6955</v>
+        <v>43.9078</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.18</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5759</v>
+        <v>0.5432</v>
       </c>
       <c r="J173" t="n">
-        <v>33.9781</v>
+        <v>32.0488</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.11</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3797</v>
+        <v>0.3571</v>
       </c>
       <c r="J174" t="n">
-        <v>22.4023</v>
+        <v>21.0689</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.93</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.339</v>
+        <v>-0.2783</v>
       </c>
       <c r="J175" t="n">
-        <v>-20.001</v>
+        <v>-16.4197</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5653</v>
+        <v>-0.5077</v>
       </c>
       <c r="J176" t="n">
-        <v>-33.3527</v>
+        <v>-29.9543</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8304</v>
+        <v>1.0247</v>
       </c>
       <c r="J177" t="n">
-        <v>48.9936</v>
+        <v>60.4573</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.14</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2663</v>
+        <v>0.3084</v>
       </c>
       <c r="J178" t="n">
-        <v>15.7117</v>
+        <v>18.1956</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.214</v>
+        <v>-0.1194</v>
       </c>
       <c r="J179" t="n">
-        <v>-12.626</v>
+        <v>-7.0446</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.88</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.28</v>
+        <v>-0.1641</v>
       </c>
       <c r="J180" t="n">
-        <v>-16.52</v>
+        <v>-9.681900000000001</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3411</v>
+        <v>-0.2064</v>
       </c>
       <c r="J181" t="n">
-        <v>-20.1249</v>
+        <v>-12.1776</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0406</v>
+        <v>1.0113</v>
       </c>
       <c r="J182" t="n">
-        <v>37.4616</v>
+        <v>36.4068</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.31</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8867</v>
+        <v>0.8627</v>
       </c>
       <c r="J183" t="n">
-        <v>31.9212</v>
+        <v>31.0572</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1933</v>
+        <v>0.2136</v>
       </c>
       <c r="J184" t="n">
-        <v>6.9588</v>
+        <v>7.6896</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4311</v>
+        <v>-0.3694</v>
       </c>
       <c r="J185" t="n">
-        <v>-15.5196</v>
+        <v>-13.2984</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.71</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.8692</v>
       </c>
       <c r="J186" t="n">
-        <v>-32.5332</v>
+        <v>-31.2912</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5503</v>
+        <v>0.659</v>
       </c>
       <c r="J187" t="n">
-        <v>19.8108</v>
+        <v>23.724</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.22</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4032</v>
+        <v>0.4669</v>
       </c>
       <c r="J188" t="n">
-        <v>14.5152</v>
+        <v>16.8084</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1645</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.922</v>
+        <v>-3.2688</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2523</v>
+        <v>-0.1482</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.082800000000001</v>
+        <v>-5.3352</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4588</v>
+        <v>-0.2912</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.5168</v>
+        <v>-10.4832</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.07</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2233</v>
+        <v>0.2208</v>
       </c>
       <c r="J192" t="n">
-        <v>6.0291</v>
+        <v>5.9616</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.04</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1662</v>
+        <v>0.1499</v>
       </c>
       <c r="J193" t="n">
-        <v>4.4874</v>
+        <v>4.0473</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.96</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0415</v>
+        <v>-0.0506</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.1205</v>
+        <v>-1.3662</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5471</v>
+        <v>-0.3589</v>
       </c>
       <c r="J195" t="n">
-        <v>-14.7717</v>
+        <v>-9.690300000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.65</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5604</v>
+        <v>-0.3683</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.1308</v>
+        <v>-9.944100000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.48</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1612</v>
+        <v>1.1064</v>
       </c>
       <c r="J197" t="n">
-        <v>31.3524</v>
+        <v>29.8728</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.43</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0577</v>
+        <v>1.0413</v>
       </c>
       <c r="J198" t="n">
-        <v>28.5579</v>
+        <v>28.1151</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.36</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9059</v>
+        <v>0.9169</v>
       </c>
       <c r="J199" t="n">
-        <v>24.4593</v>
+        <v>24.7563</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2731</v>
+        <v>0.3482</v>
       </c>
       <c r="J200" t="n">
-        <v>7.3737</v>
+        <v>9.401400000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.82</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6922</v>
+        <v>-0.6329</v>
       </c>
       <c r="J201" t="n">
-        <v>-18.6894</v>
+        <v>-17.0883</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.75</v>
       </c>
       <c r="I202" t="n">
-        <v>1.6182</v>
+        <v>1.4083</v>
       </c>
       <c r="J202" t="n">
-        <v>35.6004</v>
+        <v>30.9826</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.52</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1822</v>
+        <v>1.1333</v>
       </c>
       <c r="J203" t="n">
-        <v>26.0084</v>
+        <v>24.9326</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.31</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6901</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>15.1822</v>
+        <v>17.2656</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.19</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4042</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="J205" t="n">
-        <v>8.8924</v>
+        <v>11.055</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.06</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0585</v>
+        <v>0.1452</v>
       </c>
       <c r="J206" t="n">
-        <v>1.287</v>
+        <v>3.1944</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3393</v>
+        <v>0.3689</v>
       </c>
       <c r="J207" t="n">
-        <v>7.4646</v>
+        <v>8.1158</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.8</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.252</v>
+        <v>-0.205</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.544</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.75</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3353</v>
+        <v>-0.2546</v>
       </c>
       <c r="J209" t="n">
-        <v>-7.3766</v>
+        <v>-5.6012</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.49</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.7309</v>
+        <v>-0.4959</v>
       </c>
       <c r="J210" t="n">
-        <v>-16.0798</v>
+        <v>-10.9098</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.48</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7436</v>
+        <v>-0.5052</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.3592</v>
+        <v>-11.1144</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.2</v>
       </c>
       <c r="I212" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J212" t="n">
-        <v>53.5418</v>
+        <v>47.6788</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2942</v>
+        <v>0.372</v>
       </c>
       <c r="J213" t="n">
-        <v>7.6492</v>
+        <v>9.672000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0844</v>
+        <v>-0.0075</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.1944</v>
+        <v>-0.195</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1425</v>
+        <v>-0.0624</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.705</v>
+        <v>-1.6224</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3769</v>
+        <v>-0.2964</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.7994</v>
+        <v>-7.7064</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.16</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3417</v>
+        <v>0.3795</v>
       </c>
       <c r="J217" t="n">
-        <v>8.8842</v>
+        <v>9.867000000000001</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.03</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1141</v>
+        <v>0.1019</v>
       </c>
       <c r="J218" t="n">
-        <v>2.9666</v>
+        <v>2.6494</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0568</v>
+        <v>-0.0465</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.4768</v>
+        <v>-1.209</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1535</v>
+        <v>-0.0953</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.991</v>
+        <v>-2.4778</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.67</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5502</v>
+        <v>-0.359</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.3052</v>
+        <v>-9.334</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2574/event_2574_evp_summary.xlsx
+++ b/database/event/2574/event_2574_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3725</v>
+        <v>8.445</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9805</v>
+        <v>0.989</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1418</v>
+        <v>3.2201</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3725</v>
+        <v>8.445</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1825</v>
+        <v>4.0742</v>
       </c>
       <c r="G2" t="n">
-        <v>4.19</v>
+        <v>4.3708</v>
       </c>
       <c r="H2" t="n">
-        <v>9.2502</v>
+        <v>8.5481</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8097</v>
+        <v>4.6159</v>
       </c>
       <c r="J2" t="n">
-        <v>4.19</v>
+        <v>4.3708</v>
       </c>
       <c r="K2" t="n">
         <v>160</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>8.999700000000001</v>
+        <v>8.986699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3138</v>
+        <v>6.4229</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7522</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2124</v>
+        <v>2.2996</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3138</v>
+        <v>6.4229</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7358</v>
+        <v>2.6578</v>
       </c>
       <c r="G3" t="n">
-        <v>3.578</v>
+        <v>3.7651</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1529</v>
+        <v>3.8749</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1593</v>
+        <v>2.0924</v>
       </c>
       <c r="J3" t="n">
-        <v>3.578</v>
+        <v>3.7651</v>
       </c>
       <c r="K3" t="n">
         <v>160</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>5.737299999999999</v>
+        <v>5.8575</v>
       </c>
       <c r="N3" t="n">
         <v>264</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5709</v>
+        <v>5.7867</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6524</v>
+        <v>0.6777</v>
       </c>
       <c r="D4" t="n">
-        <v>1.877</v>
+        <v>2.01</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5709</v>
+        <v>5.7867</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2477</v>
+        <v>3.1669</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3232</v>
+        <v>2.6198</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9564</v>
+        <v>5.5547</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0971</v>
+        <v>2.9995</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3232</v>
+        <v>2.6198</v>
       </c>
       <c r="K4" t="n">
         <v>94</v>
@@ -621,7 +621,7 @@
         <v>89</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4203</v>
+        <v>5.6193</v>
       </c>
       <c r="N4" t="n">
         <v>183</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5229</v>
+        <v>4.6609</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4038</v>
+        <v>1.4975</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5229</v>
+        <v>4.6609</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0401</v>
+        <v>0.9785</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4828</v>
+        <v>3.6824</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0401</v>
+        <v>0.9785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5284</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4828</v>
+        <v>3.6824</v>
       </c>
       <c r="K5" t="n">
         <v>160</v>
@@ -667,7 +667,7 @@
         <v>104</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0236</v>
+        <v>4.2108</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1296</v>
+        <v>4.3076</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4836</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2263</v>
+        <v>1.3367</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1296</v>
+        <v>4.3076</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5836</v>
+        <v>2.5022</v>
       </c>
       <c r="G6" t="n">
-        <v>1.546</v>
+        <v>1.8054</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6167</v>
+        <v>3.3613</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8805</v>
+        <v>1.8151</v>
       </c>
       <c r="J6" t="n">
-        <v>1.546</v>
+        <v>1.8054</v>
       </c>
       <c r="K6" t="n">
         <v>94</v>
@@ -713,7 +713,7 @@
         <v>89</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4265</v>
+        <v>3.6205</v>
       </c>
       <c r="N6" t="n">
         <v>183</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.977</v>
+        <v>3.639</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4658</v>
+        <v>0.4262</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1574</v>
+        <v>1.0323</v>
       </c>
       <c r="E7" t="n">
-        <v>3.977</v>
+        <v>3.639</v>
       </c>
       <c r="F7" t="n">
-        <v>3.977</v>
+        <v>3.639</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3729</v>
+        <v>5.2396</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3729</v>
+        <v>5.2396</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3729</v>
+        <v>5.2396</v>
       </c>
       <c r="N7" t="n">
         <v>149</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2106</v>
+        <v>2.9115</v>
       </c>
       <c r="C8" t="n">
-        <v>0.376</v>
+        <v>0.341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8114</v>
+        <v>0.7012</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2106</v>
+        <v>2.9115</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2106</v>
+        <v>2.3648</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.5467</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6902</v>
+        <v>2.908</v>
       </c>
       <c r="I8" t="n">
-        <v>3.842</v>
+        <v>1.5703</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.5467</v>
       </c>
       <c r="K8" t="n">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M8" t="n">
-        <v>3.842</v>
+        <v>2.117</v>
       </c>
       <c r="N8" t="n">
-        <v>152</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9289</v>
+        <v>2.9102</v>
       </c>
       <c r="C9" t="n">
-        <v>0.343</v>
+        <v>0.3408</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6842</v>
+        <v>0.7006</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9289</v>
+        <v>2.9102</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1996</v>
+        <v>3.164</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2707</v>
+        <v>-0.2538</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7872</v>
+        <v>5.5449</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0091</v>
+        <v>2.9942</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2707</v>
+        <v>-0.2538</v>
       </c>
       <c r="K9" t="n">
         <v>94</v>
@@ -851,7 +851,7 @@
         <v>89</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7384</v>
+        <v>2.7404</v>
       </c>
       <c r="N9" t="n">
         <v>183</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9211</v>
+        <v>2.9015</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3421</v>
+        <v>0.3398</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6807</v>
+        <v>0.6966</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9211</v>
+        <v>2.9015</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4499</v>
+        <v>2.9015</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4712</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1455</v>
+        <v>3.6256</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6355</v>
+        <v>3.719</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4712</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="L10" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1067</v>
+        <v>3.719</v>
       </c>
       <c r="N10" t="n">
-        <v>183</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7291</v>
+        <v>2.6675</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3196</v>
+        <v>0.3124</v>
       </c>
       <c r="D11" t="n">
-        <v>0.594</v>
+        <v>0.5901</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7291</v>
+        <v>2.6675</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6595</v>
+        <v>2.5787</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0696</v>
+        <v>0.0888</v>
       </c>
       <c r="H11" t="n">
-        <v>3.884</v>
+        <v>3.6139</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0195</v>
+        <v>1.9515</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0696</v>
+        <v>0.0888</v>
       </c>
       <c r="K11" t="n">
         <v>94</v>
@@ -943,7 +943,7 @@
         <v>89</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0891</v>
+        <v>2.0403</v>
       </c>
       <c r="N11" t="n">
         <v>183</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4829</v>
+        <v>2.3579</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2908</v>
+        <v>0.2761</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4829</v>
+        <v>0.4492</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4829</v>
+        <v>2.3579</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5088</v>
+        <v>2.4013</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0259</v>
+        <v>-0.0434</v>
       </c>
       <c r="H12" t="n">
-        <v>3.353</v>
+        <v>3.0288</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7434</v>
+        <v>1.6355</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0259</v>
+        <v>-0.0434</v>
       </c>
       <c r="K12" t="n">
         <v>64</v>
@@ -989,7 +989,7 @@
         <v>57</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7175</v>
+        <v>1.5921</v>
       </c>
       <c r="N12" t="n">
         <v>121</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4288</v>
+        <v>2.3218</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2845</v>
+        <v>0.2719</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4585</v>
+        <v>0.4327</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4288</v>
+        <v>2.3218</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5899</v>
+        <v>-0.2822</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1611</v>
+        <v>2.604</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6388</v>
+        <v>-0.2822</v>
       </c>
       <c r="I13" t="n">
-        <v>1.892</v>
+        <v>-0.1524</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1611</v>
+        <v>2.604</v>
       </c>
       <c r="K13" t="n">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="L13" t="n">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7309</v>
+        <v>2.4516</v>
       </c>
       <c r="N13" t="n">
-        <v>121</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2145</v>
+        <v>2.3108</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2594</v>
+        <v>0.2706</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3617</v>
+        <v>0.4277</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2145</v>
+        <v>2.3108</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3639</v>
+        <v>2.481</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5784</v>
+        <v>-0.1702</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3639</v>
+        <v>3.2915</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1892</v>
+        <v>1.7774</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5784</v>
+        <v>-0.1702</v>
       </c>
       <c r="K14" t="n">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="L14" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3892</v>
+        <v>1.6072</v>
       </c>
       <c r="N14" t="n">
-        <v>264</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.181</v>
+        <v>2.1564</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2554</v>
+        <v>0.2525</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3466</v>
+        <v>0.3574</v>
       </c>
       <c r="E15" t="n">
-        <v>2.181</v>
+        <v>2.1564</v>
       </c>
       <c r="F15" t="n">
-        <v>2.181</v>
+        <v>2.1564</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.181</v>
+        <v>2.1564</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2707</v>
+        <v>2.212</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2707</v>
+        <v>2.212</v>
       </c>
       <c r="N15" t="n">
         <v>152</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5803</v>
+        <v>1.6293</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1851</v>
+        <v>0.1908</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1175</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5803</v>
+        <v>1.6293</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3334</v>
+        <v>2.4178</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7531</v>
+        <v>-0.7885</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7353</v>
+        <v>3.083</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4222</v>
+        <v>1.6648</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7531</v>
+        <v>-0.7885</v>
       </c>
       <c r="K16" t="n">
         <v>85</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6690999999999999</v>
+        <v>0.8763000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>127</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3765</v>
+        <v>1.3539</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1612</v>
+        <v>0.1586</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0166</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3765</v>
+        <v>1.3539</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3765</v>
+        <v>1.3539</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3765</v>
+        <v>1.3539</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3765</v>
+        <v>1.3539</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3765</v>
+        <v>1.3539</v>
       </c>
       <c r="N17" t="n">
         <v>149</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0465</v>
+        <v>1.0003</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1226</v>
+        <v>0.1172</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1656</v>
+        <v>-0.1688</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0465</v>
+        <v>1.0003</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1957</v>
+        <v>1.1626</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1492</v>
+        <v>-0.1623</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1957</v>
+        <v>1.1626</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6217</v>
+        <v>0.6278</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1492</v>
+        <v>-0.1623</v>
       </c>
       <c r="K18" t="n">
         <v>64</v>
@@ -1265,7 +1265,7 @@
         <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4725</v>
+        <v>0.4655</v>
       </c>
       <c r="N18" t="n">
         <v>121</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4998</v>
+        <v>0.4195</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0585</v>
+        <v>0.0491</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4124</v>
+        <v>-0.4332</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4998</v>
+        <v>0.4195</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4998</v>
+        <v>0.4195</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4998</v>
+        <v>0.4195</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4998</v>
+        <v>0.4195</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4998</v>
+        <v>0.4195</v>
       </c>
       <c r="N19" t="n">
         <v>77</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4408</v>
+        <v>0.3732</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0516</v>
+        <v>0.0437</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.439</v>
+        <v>-0.4543</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4408</v>
+        <v>0.3732</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4022</v>
+        <v>1.3539</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9614</v>
+        <v>-0.9807</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4022</v>
+        <v>1.3539</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7291</v>
+        <v>0.7311</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9614</v>
+        <v>-0.9807</v>
       </c>
       <c r="K20" t="n">
         <v>85</v>
@@ -1357,7 +1357,7 @@
         <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2323000000000001</v>
+        <v>-0.2496</v>
       </c>
       <c r="N20" t="n">
         <v>127</v>
@@ -1366,32 +1366,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4369</v>
+        <v>0.3732</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0512</v>
+        <v>0.0437</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4408</v>
+        <v>-0.4543</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4369</v>
+        <v>0.3732</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4369</v>
+        <v>0.3732</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4369</v>
+        <v>0.3732</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4369</v>
+        <v>0.3732</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4369</v>
+        <v>0.3732</v>
       </c>
       <c r="N21" t="n">
         <v>149</v>
@@ -1412,32 +1412,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3978</v>
+        <v>0.3712</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0466</v>
+        <v>0.0435</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4584</v>
+        <v>-0.4552</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3978</v>
+        <v>0.3712</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3978</v>
+        <v>0.3712</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3978</v>
+        <v>0.3712</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3978</v>
+        <v>0.3712</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3978</v>
+        <v>0.3712</v>
       </c>
       <c r="N22" t="n">
         <v>149</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2954</v>
+        <v>0.2808</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0346</v>
+        <v>0.0329</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5047</v>
+        <v>-0.4964</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2954</v>
+        <v>0.2808</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2954</v>
+        <v>0.2808</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2954</v>
+        <v>0.2808</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3076</v>
+        <v>0.288</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3076</v>
+        <v>0.288</v>
       </c>
       <c r="N23" t="n">
         <v>152</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2488</v>
+        <v>0.1838</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0291</v>
+        <v>0.0215</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.5405</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2488</v>
+        <v>0.1838</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0303</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7815</v>
+        <v>-0.8157</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0303</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5357</v>
+        <v>0.5397</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7815</v>
+        <v>-0.8157</v>
       </c>
       <c r="K24" t="n">
         <v>85</v>
@@ -1541,7 +1541,7 @@
         <v>42</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2458</v>
+        <v>-0.276</v>
       </c>
       <c r="N24" t="n">
         <v>127</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1754</v>
+        <v>0.1468</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0205</v>
+        <v>0.0172</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5588</v>
+        <v>-0.5574</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1754</v>
+        <v>0.1468</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1754</v>
+        <v>0.1468</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1754</v>
+        <v>0.1468</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1754</v>
+        <v>0.1468</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1754</v>
+        <v>0.1468</v>
       </c>
       <c r="N25" t="n">
         <v>91</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.095</v>
+        <v>0.0138</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0111</v>
+        <v>0.0016</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5951</v>
+        <v>-0.6179</v>
       </c>
       <c r="E26" t="n">
-        <v>0.095</v>
+        <v>0.0138</v>
       </c>
       <c r="F26" t="n">
-        <v>0.095</v>
+        <v>0.0138</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.095</v>
+        <v>0.0138</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0989</v>
+        <v>0.0138</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0989</v>
+        <v>0.0138</v>
       </c>
       <c r="N26" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0574</v>
+        <v>-0.0041</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0067</v>
+        <v>-0.0005</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6121</v>
+        <v>-0.6261</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0574</v>
+        <v>-0.0041</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0574</v>
+        <v>-0.0041</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0574</v>
+        <v>-0.0041</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0574</v>
+        <v>-0.0042</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0574</v>
+        <v>-0.0042</v>
       </c>
       <c r="N27" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0072</v>
+        <v>-0.0474</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0008</v>
+        <v>-0.0056</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6413</v>
+        <v>-0.6458</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0072</v>
+        <v>-0.0474</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3173</v>
+        <v>0.3076</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3245</v>
+        <v>-0.355</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3173</v>
+        <v>0.3076</v>
       </c>
       <c r="I28" t="n">
-        <v>0.165</v>
+        <v>0.1661</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3245</v>
+        <v>-0.355</v>
       </c>
       <c r="K28" t="n">
         <v>64</v>
@@ -1725,7 +1725,7 @@
         <v>57</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1595</v>
+        <v>-0.1889</v>
       </c>
       <c r="N28" t="n">
         <v>121</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0256</v>
+        <v>-0.12</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.003</v>
+        <v>-0.0141</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6496</v>
+        <v>-0.6788</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0256</v>
+        <v>-0.12</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8612</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.8868</v>
+        <v>-0.9048</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8612</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4478</v>
+        <v>0.4238</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8868</v>
+        <v>-0.9048</v>
       </c>
       <c r="K29" t="n">
         <v>85</v>
@@ -1771,7 +1771,7 @@
         <v>42</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4390000000000001</v>
+        <v>-0.481</v>
       </c>
       <c r="N29" t="n">
         <v>127</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1337</v>
+        <v>-0.1545</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0157</v>
+        <v>-0.0181</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6984</v>
+        <v>-0.6945</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1337</v>
+        <v>-0.1545</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1337</v>
+        <v>-0.1545</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1337</v>
+        <v>-0.1545</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1337</v>
+        <v>-0.1545</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1337</v>
+        <v>-0.1545</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1789</v>
+        <v>-0.2012</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.021</v>
+        <v>-0.0236</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7188</v>
+        <v>-0.7158</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1789</v>
+        <v>-0.2012</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1789</v>
+        <v>-0.2012</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1789</v>
+        <v>-0.2012</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1789</v>
+        <v>-0.2012</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1789</v>
+        <v>-0.2012</v>
       </c>
       <c r="N31" t="n">
         <v>91</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2593</v>
+        <v>-0.2343</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0304</v>
+        <v>-0.0274</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7551</v>
+        <v>-0.7309</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2593</v>
+        <v>-0.2343</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2593</v>
+        <v>-0.2343</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2593</v>
+        <v>-0.2343</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.27</v>
+        <v>-0.2403</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.27</v>
+        <v>-0.2403</v>
       </c>
       <c r="N32" t="n">
         <v>152</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3016</v>
+        <v>-0.3342</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0353</v>
+        <v>-0.0391</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7742</v>
+        <v>-0.7763</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3016</v>
+        <v>-0.3342</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3016</v>
+        <v>-0.3342</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3016</v>
+        <v>-0.3342</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3016</v>
+        <v>-0.3342</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3016</v>
+        <v>-0.3342</v>
       </c>
       <c r="N33" t="n">
         <v>77</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4666</v>
+        <v>-0.495</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0546</v>
+        <v>-0.058</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8487</v>
+        <v>-0.8495</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4666</v>
+        <v>-0.495</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4666</v>
+        <v>-0.495</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4666</v>
+        <v>-0.495</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4666</v>
+        <v>-0.495</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4666</v>
+        <v>-0.495</v>
       </c>
       <c r="N34" t="n">
         <v>77</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4936</v>
+        <v>-0.5258</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0578</v>
+        <v>-0.0616</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8609</v>
+        <v>-0.8636</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4936</v>
+        <v>-0.5258</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4936</v>
+        <v>-0.5258</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4936</v>
+        <v>-0.5258</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4936</v>
+        <v>-0.5258</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4936</v>
+        <v>-0.5258</v>
       </c>
       <c r="N35" t="n">
         <v>77</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dazzLe</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.83</v>
+        <v>-0.7532</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0882</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0127</v>
+        <v>-0.9671</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.83</v>
+        <v>-0.7532</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.83</v>
+        <v>-1.1195</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.3663</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.83</v>
+        <v>-1.1195</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.83</v>
+        <v>-0.6045</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.3663</v>
       </c>
       <c r="K36" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.83</v>
+        <v>-0.2382</v>
       </c>
       <c r="N36" t="n">
-        <v>77</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8928</v>
+        <v>-0.8457</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1046</v>
+        <v>-0.099</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0411</v>
+        <v>-1.0092</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8928</v>
+        <v>-0.8457</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0964</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2036</v>
+        <v>0.1276</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0964</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.5256</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2036</v>
+        <v>0.1276</v>
       </c>
       <c r="K37" t="n">
         <v>85</v>
@@ -2139,7 +2139,7 @@
         <v>42</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.3665</v>
+        <v>-0.398</v>
       </c>
       <c r="N37" t="n">
         <v>127</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>dazzLe</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0011</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1172</v>
+        <v>-0.1034</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.09</v>
+        <v>-1.026</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0011</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3242</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3231</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3242</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6885</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3231</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="L38" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.3654</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1944</v>
+        <v>-1.2467</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1399</v>
+        <v>-0.146</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1772</v>
+        <v>-1.1917</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1944</v>
+        <v>-1.2467</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1944</v>
+        <v>-1.2467</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1944</v>
+        <v>-1.2467</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1944</v>
+        <v>-1.2467</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1944</v>
+        <v>-1.2467</v>
       </c>
       <c r="N39" t="n">
         <v>91</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3902</v>
+        <v>-1.3984</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1628</v>
+        <v>-0.1638</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2656</v>
+        <v>-1.2608</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3902</v>
+        <v>-1.3984</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3902</v>
+        <v>-1.3984</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3902</v>
+        <v>-1.3984</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3902</v>
+        <v>-1.3984</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3902</v>
+        <v>-1.3984</v>
       </c>
       <c r="N40" t="n">
         <v>149</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.9801</v>
+        <v>-2.9121</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.349</v>
+        <v>-0.3411</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9834</v>
+        <v>-1.9499</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.9801</v>
+        <v>-2.9121</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9801</v>
+        <v>-0.9558</v>
       </c>
       <c r="G41" t="n">
-        <v>-2</v>
+        <v>-1.9563</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9801</v>
+        <v>-0.9558</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.5161</v>
       </c>
       <c r="J41" t="n">
-        <v>-2</v>
+        <v>-1.9563</v>
       </c>
       <c r="K41" t="n">
         <v>160</v>
@@ -2323,7 +2323,7 @@
         <v>104</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.5096</v>
+        <v>-2.4724</v>
       </c>
       <c r="N41" t="n">
         <v>264</v>
@@ -2429,10 +2429,10 @@
         <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8608</v>
+        <v>1.8453</v>
       </c>
       <c r="J2" t="n">
-        <v>37.216</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2096</v>
+        <v>1.253</v>
       </c>
       <c r="J3" t="n">
-        <v>24.192</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.48</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0709</v>
+        <v>1.0496</v>
       </c>
       <c r="J4" t="n">
-        <v>21.418</v>
+        <v>20.992</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.39</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9329</v>
+        <v>0.8875</v>
       </c>
       <c r="J5" t="n">
-        <v>18.658</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6049</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.098</v>
+        <v>-11.018</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1377</v>
+        <v>-0.1626</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.754</v>
+        <v>-3.252</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.83</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1602</v>
+        <v>-0.1848</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.204</v>
+        <v>-3.696</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.65</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3384</v>
+        <v>-0.3581</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.768</v>
+        <v>-7.162</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.52</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.459</v>
+        <v>-0.4725</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.18</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4777</v>
+        <v>-0.4901</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.554</v>
+        <v>-9.802</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.72</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3905</v>
+        <v>1.4983</v>
       </c>
       <c r="J12" t="n">
-        <v>37.5435</v>
+        <v>40.4541</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1587</v>
+        <v>1.1701</v>
       </c>
       <c r="J13" t="n">
-        <v>31.2849</v>
+        <v>31.5927</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.26</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6854</v>
+        <v>0.6607</v>
       </c>
       <c r="J14" t="n">
-        <v>18.5058</v>
+        <v>17.8389</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3905</v>
+        <v>0.3956</v>
       </c>
       <c r="J15" t="n">
-        <v>10.5435</v>
+        <v>10.6812</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.67</v>
+        <v>-0.617</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.09</v>
+        <v>-16.659</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2715</v>
+        <v>0.2561</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3305</v>
+        <v>6.9147</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.92</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.081</v>
+        <v>-0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.187</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3437</v>
+        <v>-0.3604</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.2799</v>
+        <v>-9.7308</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4</v>
+        <v>-0.4142</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.8</v>
+        <v>-11.1834</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4093</v>
+        <v>-0.4231</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.0511</v>
+        <v>-11.4237</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.83</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1841</v>
+        <v>-0.2033</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.6025</v>
+        <v>-5.0825</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1841</v>
+        <v>-0.2033</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.6025</v>
+        <v>-5.0825</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2418</v>
+        <v>-0.2609</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.045</v>
+        <v>-6.5225</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2606</v>
+        <v>-0.2794</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.515</v>
+        <v>-6.985</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.73</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2795</v>
+        <v>-0.2979</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.9875</v>
+        <v>-7.4475</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.76</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1664</v>
+        <v>1.2784</v>
       </c>
       <c r="J27" t="n">
-        <v>29.16</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6969</v>
+        <v>0.7754</v>
       </c>
       <c r="J28" t="n">
-        <v>17.4225</v>
+        <v>19.385</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.414</v>
+        <v>0.4593</v>
       </c>
       <c r="J29" t="n">
-        <v>10.35</v>
+        <v>11.4825</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.06</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1634</v>
+        <v>0.1852</v>
       </c>
       <c r="J30" t="n">
-        <v>4.085</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.06</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1634</v>
+        <v>0.1852</v>
       </c>
       <c r="J31" t="n">
-        <v>4.085</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3877</v>
+        <v>0.3309</v>
       </c>
       <c r="J32" t="n">
-        <v>6.5909</v>
+        <v>5.6253</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.42</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5113</v>
+        <v>-0.5276</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.6921</v>
+        <v>-8.969200000000001</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.41</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5209</v>
+        <v>-0.5363</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.8553</v>
+        <v>-9.117100000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.25</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6819</v>
+        <v>-0.6828</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.5923</v>
+        <v>-11.6076</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.23</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7027</v>
+        <v>-0.7015</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.9459</v>
+        <v>-11.9255</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.57</v>
       </c>
       <c r="I37" t="n">
-        <v>1.9551</v>
+        <v>2.1127</v>
       </c>
       <c r="J37" t="n">
-        <v>33.2367</v>
+        <v>35.9159</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>2.26</v>
       </c>
       <c r="I38" t="n">
-        <v>1.6334</v>
+        <v>1.7807</v>
       </c>
       <c r="J38" t="n">
-        <v>27.7678</v>
+        <v>30.2719</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5386</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>9.1562</v>
+        <v>10.3768</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.14</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3136</v>
+        <v>0.3422</v>
       </c>
       <c r="J40" t="n">
-        <v>5.3312</v>
+        <v>5.8174</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.08</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1474</v>
+        <v>0.1884</v>
       </c>
       <c r="J41" t="n">
-        <v>2.5058</v>
+        <v>3.2028</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3028</v>
+        <v>0.2984</v>
       </c>
       <c r="J42" t="n">
-        <v>8.175599999999999</v>
+        <v>8.056800000000001</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.17</v>
+        <v>0.1702</v>
       </c>
       <c r="J43" t="n">
-        <v>4.59</v>
+        <v>4.5954</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1235</v>
+        <v>-0.1387</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.3345</v>
+        <v>-3.7449</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2353</v>
+        <v>-0.2516</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.3531</v>
+        <v>-6.7932</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4258</v>
+        <v>-0.436</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.4966</v>
+        <v>-11.772</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.052</v>
+        <v>1.1563</v>
       </c>
       <c r="J47" t="n">
-        <v>28.404</v>
+        <v>31.2201</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.29</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5829</v>
+        <v>0.6489</v>
       </c>
       <c r="J48" t="n">
-        <v>15.7383</v>
+        <v>17.5203</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.21</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4753</v>
+        <v>0.5282</v>
       </c>
       <c r="J49" t="n">
-        <v>12.8331</v>
+        <v>14.2614</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.19</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4465</v>
+        <v>0.4958</v>
       </c>
       <c r="J50" t="n">
-        <v>12.0555</v>
+        <v>13.3866</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.96</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2322</v>
+        <v>-0.216</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.2694</v>
+        <v>-5.832</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.34</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5584</v>
+        <v>0.6179</v>
       </c>
       <c r="J52" t="n">
-        <v>16.752</v>
+        <v>18.537</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2647</v>
+        <v>0.2658</v>
       </c>
       <c r="J53" t="n">
-        <v>7.941</v>
+        <v>7.974</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.201</v>
+        <v>-0.2163</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.03</v>
+        <v>-6.489</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.71</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3192</v>
+        <v>-0.3325</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.576000000000001</v>
+        <v>-9.975</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3287</v>
+        <v>-0.3418</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.861000000000001</v>
+        <v>-10.254</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.52</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8888</v>
+        <v>0.9804</v>
       </c>
       <c r="J57" t="n">
-        <v>26.664</v>
+        <v>29.412</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.4</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.8138</v>
       </c>
       <c r="J58" t="n">
-        <v>22.032</v>
+        <v>24.414</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.28</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5749</v>
+        <v>0.6387</v>
       </c>
       <c r="J59" t="n">
-        <v>17.247</v>
+        <v>19.161</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3772</v>
+        <v>0.4069</v>
       </c>
       <c r="J60" t="n">
-        <v>11.316</v>
+        <v>12.207</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.7403</v>
       </c>
       <c r="J61" t="n">
-        <v>-24.177</v>
+        <v>-22.209</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.51</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1348</v>
+        <v>1.1008</v>
       </c>
       <c r="J62" t="n">
-        <v>28.37</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7743</v>
+        <v>0.7398</v>
       </c>
       <c r="J63" t="n">
-        <v>19.3575</v>
+        <v>18.495</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.29</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7526</v>
+        <v>0.7205</v>
       </c>
       <c r="J64" t="n">
-        <v>18.815</v>
+        <v>18.0125</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6399</v>
+        <v>0.62</v>
       </c>
       <c r="J65" t="n">
-        <v>15.9975</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2818</v>
+        <v>0.2959</v>
       </c>
       <c r="J66" t="n">
-        <v>7.045</v>
+        <v>7.3975</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3355</v>
+        <v>0.3224</v>
       </c>
       <c r="J67" t="n">
-        <v>8.387499999999999</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.148</v>
+        <v>0.1409</v>
       </c>
       <c r="J68" t="n">
-        <v>3.7</v>
+        <v>3.5225</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.05</v>
+        <v>0.0362</v>
       </c>
       <c r="J69" t="n">
-        <v>1.25</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3883</v>
+        <v>-0.4019</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.7075</v>
+        <v>-10.0475</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.32</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6629</v>
+        <v>-0.6596</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.5725</v>
+        <v>-16.49</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.95</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6245</v>
+        <v>1.6252</v>
       </c>
       <c r="J72" t="n">
-        <v>30.8655</v>
+        <v>30.8788</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.49</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0888</v>
+        <v>1.0549</v>
       </c>
       <c r="J73" t="n">
-        <v>20.6872</v>
+        <v>20.0431</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.36</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8834</v>
+        <v>0.8404</v>
       </c>
       <c r="J74" t="n">
-        <v>16.7846</v>
+        <v>15.9676</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.18</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4645</v>
+        <v>0.4688</v>
       </c>
       <c r="J75" t="n">
-        <v>8.8255</v>
+        <v>8.9072</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.15</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3873</v>
+        <v>0.399</v>
       </c>
       <c r="J76" t="n">
-        <v>7.3587</v>
+        <v>7.581</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.37</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8954</v>
+        <v>0.8235</v>
       </c>
       <c r="J77" t="n">
-        <v>17.0126</v>
+        <v>15.6465</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0514</v>
+        <v>-0.0706</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.9766</v>
+        <v>-1.3414</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.52</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4719</v>
+        <v>-0.4826</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.966100000000001</v>
+        <v>-9.1694</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.509</v>
+        <v>-0.5175</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.670999999999999</v>
+        <v>-9.8325</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.44</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.546</v>
+        <v>-0.552</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.374</v>
+        <v>-10.488</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3702</v>
+        <v>1.3514</v>
       </c>
       <c r="J82" t="n">
-        <v>28.7742</v>
+        <v>28.3794</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.48</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0991</v>
+        <v>1.0615</v>
       </c>
       <c r="J83" t="n">
-        <v>23.0811</v>
+        <v>22.2915</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.37</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.8764</v>
       </c>
       <c r="J84" t="n">
-        <v>19.5069</v>
+        <v>18.4044</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3328</v>
+        <v>-0.3104</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.9888</v>
+        <v>-6.5184</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.91</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.393</v>
+        <v>-0.3663</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.253</v>
+        <v>-7.6923</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6519</v>
+        <v>0.6079</v>
       </c>
       <c r="J87" t="n">
-        <v>13.6899</v>
+        <v>12.7659</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.79</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2217</v>
+        <v>-0.2413</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.6557</v>
+        <v>-5.0673</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3622</v>
+        <v>-0.3782</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.6062</v>
+        <v>-7.9422</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3622</v>
+        <v>-0.3782</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.6062</v>
+        <v>-7.9422</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4835</v>
+        <v>-0.4932</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.1535</v>
+        <v>-10.3572</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5654</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>14.135</v>
+        <v>13.8475</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2048</v>
+        <v>0.2135</v>
       </c>
       <c r="J93" t="n">
-        <v>5.12</v>
+        <v>5.3375</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.9</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1338</v>
+        <v>-0.1466</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.345</v>
+        <v>-3.665</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.82</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2184</v>
+        <v>-0.232</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.46</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2584</v>
+        <v>-0.2717</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.46</v>
+        <v>-6.7925</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5542</v>
+        <v>0.5569</v>
       </c>
       <c r="J97" t="n">
-        <v>13.855</v>
+        <v>13.9225</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4378</v>
+        <v>0.4471</v>
       </c>
       <c r="J98" t="n">
-        <v>10.945</v>
+        <v>11.1775</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3658</v>
+        <v>0.3783</v>
       </c>
       <c r="J99" t="n">
-        <v>9.145</v>
+        <v>9.4575</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0873</v>
+        <v>-0.0949</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.1825</v>
+        <v>-2.3725</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4396</v>
+        <v>-0.4454</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.99</v>
+        <v>-11.135</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.55</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2494</v>
+        <v>1.2116</v>
       </c>
       <c r="J102" t="n">
-        <v>34.9832</v>
+        <v>33.9248</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.21</v>
       </c>
       <c r="I103" t="n">
-        <v>0.622</v>
+        <v>0.5929</v>
       </c>
       <c r="J103" t="n">
-        <v>17.416</v>
+        <v>16.6012</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.95</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2133</v>
+        <v>-0.2114</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.9724</v>
+        <v>-5.9192</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5863</v>
+        <v>-0.5531</v>
       </c>
       <c r="J105" t="n">
-        <v>-16.4164</v>
+        <v>-15.4868</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7159</v>
+        <v>-0.668</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.0452</v>
+        <v>-18.704</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5085</v>
+        <v>0.4987</v>
       </c>
       <c r="J107" t="n">
-        <v>14.238</v>
+        <v>13.9636</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.11</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2646</v>
+        <v>0.2704</v>
       </c>
       <c r="J108" t="n">
-        <v>7.4088</v>
+        <v>7.5712</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0368</v>
+        <v>0.0427</v>
       </c>
       <c r="J109" t="n">
-        <v>1.0304</v>
+        <v>1.1956</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.87</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1678</v>
+        <v>-0.1809</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.6984</v>
+        <v>-5.0652</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2299</v>
+        <v>-0.2432</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.4372</v>
+        <v>-6.8096</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.8</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2105</v>
+        <v>-0.2304</v>
       </c>
       <c r="J112" t="n">
-        <v>-4.631</v>
+        <v>-5.0688</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.79</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2204</v>
+        <v>-0.2402</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.8488</v>
+        <v>-5.2844</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2301</v>
+        <v>-0.2498</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.0622</v>
+        <v>-5.4956</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.77</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2396</v>
+        <v>-0.2593</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.2712</v>
+        <v>-5.7046</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.64</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3607</v>
+        <v>-0.377</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.9354</v>
+        <v>-8.294</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4852</v>
+        <v>1.4794</v>
       </c>
       <c r="J117" t="n">
-        <v>32.6744</v>
+        <v>32.5468</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.4048</v>
+        <v>1.3944</v>
       </c>
       <c r="J118" t="n">
-        <v>30.9056</v>
+        <v>30.6768</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.66</v>
       </c>
       <c r="I119" t="n">
-        <v>1.2886</v>
+        <v>1.2709</v>
       </c>
       <c r="J119" t="n">
-        <v>28.3492</v>
+        <v>27.9598</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.12</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3043</v>
+        <v>0.3239</v>
       </c>
       <c r="J120" t="n">
-        <v>6.6946</v>
+        <v>7.1258</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6728</v>
+        <v>-0.6141</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.8016</v>
+        <v>-13.5102</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5875</v>
+        <v>0.5901</v>
       </c>
       <c r="J122" t="n">
-        <v>14.1</v>
+        <v>14.1624</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.36</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4744</v>
+        <v>0.4837</v>
       </c>
       <c r="J123" t="n">
-        <v>11.3856</v>
+        <v>11.6088</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2604</v>
+        <v>0.2773</v>
       </c>
       <c r="J124" t="n">
-        <v>6.2496</v>
+        <v>6.6552</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.11</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1705</v>
+        <v>0.1876</v>
       </c>
       <c r="J125" t="n">
-        <v>4.092</v>
+        <v>4.5024</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3525</v>
+        <v>-0.3605</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.651999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.53</v>
       </c>
       <c r="I127" t="n">
-        <v>0.775</v>
+        <v>0.7438</v>
       </c>
       <c r="J127" t="n">
-        <v>18.6</v>
+        <v>17.8512</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1099</v>
+        <v>0.1182</v>
       </c>
       <c r="J128" t="n">
-        <v>2.6376</v>
+        <v>2.8368</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1856</v>
+        <v>-0.1997</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.4544</v>
+        <v>-4.7928</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2063</v>
+        <v>-0.2204</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.9512</v>
+        <v>-5.2896</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3902</v>
+        <v>-0.4002</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.364800000000001</v>
+        <v>-9.604799999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.17</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4115</v>
+        <v>0.4028</v>
       </c>
       <c r="J132" t="n">
-        <v>9.464499999999999</v>
+        <v>9.2644</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1361</v>
+        <v>0.1391</v>
       </c>
       <c r="J133" t="n">
-        <v>3.1303</v>
+        <v>3.1993</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0549</v>
+        <v>0.0557</v>
       </c>
       <c r="J134" t="n">
-        <v>1.2627</v>
+        <v>1.2811</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1256</v>
+        <v>-0.1403</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.8888</v>
+        <v>-3.2269</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.47</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5383</v>
+        <v>-0.542</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.3809</v>
+        <v>-12.466</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3401</v>
+        <v>1.3185</v>
       </c>
       <c r="J137" t="n">
-        <v>30.8223</v>
+        <v>30.3255</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.38</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9549</v>
+        <v>0.8999</v>
       </c>
       <c r="J138" t="n">
-        <v>21.9627</v>
+        <v>20.6977</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.24</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6458</v>
+        <v>0.624</v>
       </c>
       <c r="J139" t="n">
-        <v>14.8534</v>
+        <v>14.352</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.04</v>
       </c>
       <c r="I140" t="n">
-        <v>0.106</v>
+        <v>0.1286</v>
       </c>
       <c r="J140" t="n">
-        <v>2.438</v>
+        <v>2.9578</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2959</v>
+        <v>-0.2771</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.8057</v>
+        <v>-6.3733</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9548</v>
+        <v>0.9022</v>
       </c>
       <c r="J142" t="n">
-        <v>28.644</v>
+        <v>27.066</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0011</v>
+        <v>0.0007</v>
       </c>
       <c r="J143" t="n">
-        <v>0.033</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1868</v>
+        <v>-0.2006</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.604</v>
+        <v>-6.018</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.83</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2075</v>
+        <v>-0.2213</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.225</v>
+        <v>-6.639</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2676</v>
+        <v>-0.2809</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.028</v>
+        <v>-8.427</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0483</v>
+        <v>0.9925</v>
       </c>
       <c r="J147" t="n">
-        <v>31.449</v>
+        <v>29.775</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.2</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5825</v>
+        <v>0.5605</v>
       </c>
       <c r="J148" t="n">
-        <v>17.475</v>
+        <v>16.815</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.532</v>
+        <v>0.5153</v>
       </c>
       <c r="J149" t="n">
-        <v>15.96</v>
+        <v>15.459</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.98</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1193</v>
+        <v>-0.1171</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.579</v>
+        <v>-3.513</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8028</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-24.084</v>
+        <v>-22.272</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2034</v>
+        <v>-0.231</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.2714</v>
+        <v>-4.851</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.59</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3817</v>
+        <v>-0.4017</v>
       </c>
       <c r="J153" t="n">
-        <v>-8.015700000000001</v>
+        <v>-8.435700000000001</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.57</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3994</v>
+        <v>-0.4186</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.3874</v>
+        <v>-8.7906</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4085</v>
+        <v>-0.4271</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.5785</v>
+        <v>-8.969099999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.49</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4736</v>
+        <v>-0.4883</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.945600000000001</v>
+        <v>-10.2543</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.85</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4998</v>
+        <v>1.4961</v>
       </c>
       <c r="J157" t="n">
-        <v>31.4958</v>
+        <v>31.4181</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2822</v>
+        <v>1.2653</v>
       </c>
       <c r="J158" t="n">
-        <v>26.9262</v>
+        <v>26.5713</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8954</v>
+        <v>0.8528</v>
       </c>
       <c r="J159" t="n">
-        <v>18.8034</v>
+        <v>17.9088</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.26</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6482</v>
+        <v>0.635</v>
       </c>
       <c r="J160" t="n">
-        <v>13.6122</v>
+        <v>13.335</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.25</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6246</v>
+        <v>0.6141</v>
       </c>
       <c r="J161" t="n">
-        <v>13.1166</v>
+        <v>12.8961</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5727</v>
       </c>
       <c r="J162" t="n">
-        <v>16.8084</v>
+        <v>16.0356</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.85</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1739</v>
+        <v>-0.1907</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.8692</v>
+        <v>-5.3396</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.77</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2537</v>
+        <v>-0.27</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.1036</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2537</v>
+        <v>-0.27</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.1036</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2829</v>
+        <v>-0.2986</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.9212</v>
+        <v>-8.360799999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8807</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>24.6596</v>
+        <v>23.2428</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.34</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8807</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>24.6596</v>
+        <v>23.2428</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5344</v>
+        <v>0.5224</v>
       </c>
       <c r="J169" t="n">
-        <v>14.9632</v>
+        <v>14.6272</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.14</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4081</v>
+        <v>0.4078</v>
       </c>
       <c r="J170" t="n">
-        <v>11.4268</v>
+        <v>11.4184</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1807</v>
+        <v>0.1973</v>
       </c>
       <c r="J171" t="n">
-        <v>5.0596</v>
+        <v>5.5244</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7442</v>
+        <v>0.7012</v>
       </c>
       <c r="J172" t="n">
-        <v>43.9078</v>
+        <v>41.3708</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.18</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5432</v>
+        <v>0.5231</v>
       </c>
       <c r="J173" t="n">
-        <v>32.0488</v>
+        <v>30.8629</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.11</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3571</v>
+        <v>0.3541</v>
       </c>
       <c r="J174" t="n">
-        <v>21.0689</v>
+        <v>20.8919</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.93</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2783</v>
+        <v>-0.2722</v>
       </c>
       <c r="J175" t="n">
-        <v>-16.4197</v>
+        <v>-16.0598</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5077</v>
+        <v>-0.4824</v>
       </c>
       <c r="J176" t="n">
-        <v>-29.9543</v>
+        <v>-28.4616</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0247</v>
+        <v>0.982</v>
       </c>
       <c r="J177" t="n">
-        <v>60.4573</v>
+        <v>57.938</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.14</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3084</v>
+        <v>0.3155</v>
       </c>
       <c r="J178" t="n">
-        <v>18.1956</v>
+        <v>18.6145</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1194</v>
+        <v>-0.1297</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.0446</v>
+        <v>-7.6523</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.88</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1641</v>
+        <v>-0.1755</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.681900000000001</v>
+        <v>-10.3545</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2064</v>
+        <v>-0.2182</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.1776</v>
+        <v>-12.8738</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0113</v>
+        <v>0.9473</v>
       </c>
       <c r="J182" t="n">
-        <v>36.4068</v>
+        <v>34.1028</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.31</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8627</v>
+        <v>0.8054</v>
       </c>
       <c r="J183" t="n">
-        <v>31.0572</v>
+        <v>28.9944</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2136</v>
+        <v>0.22</v>
       </c>
       <c r="J184" t="n">
-        <v>7.6896</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3694</v>
+        <v>-0.3563</v>
       </c>
       <c r="J185" t="n">
-        <v>-13.2984</v>
+        <v>-12.8268</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.71</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.8692</v>
+        <v>-0.8018</v>
       </c>
       <c r="J186" t="n">
-        <v>-31.2912</v>
+        <v>-28.8648</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.659</v>
+        <v>0.637</v>
       </c>
       <c r="J187" t="n">
-        <v>23.724</v>
+        <v>22.932</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.22</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4669</v>
+        <v>0.4614</v>
       </c>
       <c r="J188" t="n">
-        <v>16.8084</v>
+        <v>16.6104</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.1011</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.2688</v>
+        <v>-3.6396</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1482</v>
+        <v>-0.1605</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.3352</v>
+        <v>-5.778</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2912</v>
+        <v>-0.3033</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.4832</v>
+        <v>-10.9188</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.07</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2208</v>
+        <v>0.2187</v>
       </c>
       <c r="J192" t="n">
-        <v>5.9616</v>
+        <v>5.9049</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.04</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1499</v>
+        <v>0.1491</v>
       </c>
       <c r="J193" t="n">
-        <v>4.0473</v>
+        <v>4.0257</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.96</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0506</v>
+        <v>-0.0629</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.3662</v>
+        <v>-1.6983</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3589</v>
+        <v>-0.3723</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.690300000000001</v>
+        <v>-10.0521</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.65</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3683</v>
+        <v>-0.3814</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.944100000000001</v>
+        <v>-10.2978</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.48</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1064</v>
+        <v>1.0681</v>
       </c>
       <c r="J197" t="n">
-        <v>29.8728</v>
+        <v>28.8387</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.43</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0413</v>
+        <v>0.992</v>
       </c>
       <c r="J198" t="n">
-        <v>28.1151</v>
+        <v>26.784</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.36</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9169</v>
+        <v>0.8637</v>
       </c>
       <c r="J199" t="n">
-        <v>24.7563</v>
+        <v>23.3199</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3482</v>
+        <v>0.3545</v>
       </c>
       <c r="J200" t="n">
-        <v>9.401400000000001</v>
+        <v>9.5715</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.82</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6329</v>
+        <v>-0.5859</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.0883</v>
+        <v>-15.8193</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.75</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4083</v>
+        <v>1.3955</v>
       </c>
       <c r="J202" t="n">
-        <v>30.9826</v>
+        <v>30.701</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.52</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1333</v>
+        <v>1.102</v>
       </c>
       <c r="J203" t="n">
-        <v>24.9326</v>
+        <v>24.244</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.31</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>17.2656</v>
+        <v>16.533</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.19</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5004</v>
       </c>
       <c r="J205" t="n">
-        <v>11.055</v>
+        <v>11.0088</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.06</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1452</v>
+        <v>0.1725</v>
       </c>
       <c r="J206" t="n">
-        <v>3.1944</v>
+        <v>3.795</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3689</v>
+        <v>0.3427</v>
       </c>
       <c r="J207" t="n">
-        <v>8.1158</v>
+        <v>7.5394</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.8</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.205</v>
+        <v>-0.2262</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.51</v>
+        <v>-4.9764</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.75</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2546</v>
+        <v>-0.2749</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.6012</v>
+        <v>-6.0478</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.49</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4959</v>
+        <v>-0.5057</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.9098</v>
+        <v>-11.1254</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.48</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5052</v>
+        <v>-0.5145</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.1144</v>
+        <v>-11.319</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.2</v>
       </c>
       <c r="I212" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J212" t="n">
-        <v>47.6788</v>
+        <v>50.3672</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.372</v>
+        <v>0.377</v>
       </c>
       <c r="J213" t="n">
-        <v>9.672000000000001</v>
+        <v>9.802</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0075</v>
+        <v>0.0166</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.195</v>
+        <v>0.4316</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0624</v>
+        <v>-0.0432</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.6224</v>
+        <v>-1.1232</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2964</v>
+        <v>-0.2774</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.7064</v>
+        <v>-7.2124</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.16</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3795</v>
+        <v>0.3754</v>
       </c>
       <c r="J217" t="n">
-        <v>9.867000000000001</v>
+        <v>9.760400000000001</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.03</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1019</v>
+        <v>0.1073</v>
       </c>
       <c r="J218" t="n">
-        <v>2.6494</v>
+        <v>2.7898</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0465</v>
+        <v>-0.0556</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.209</v>
+        <v>-1.4456</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0953</v>
+        <v>-0.1079</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.4778</v>
+        <v>-2.8054</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.67</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.359</v>
+        <v>-0.3707</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.334</v>
+        <v>-9.638199999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2574/event_2574_evp_summary.xlsx
+++ b/database/event/2574/event_2574_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.445</v>
+        <v>8.359</v>
       </c>
       <c r="C2" t="n">
-        <v>0.989</v>
+        <v>0.979</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2201</v>
+        <v>3.2021</v>
       </c>
       <c r="E2" t="n">
-        <v>8.445</v>
+        <v>8.359</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0742</v>
+        <v>3.8969</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3708</v>
+        <v>4.4621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5481</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6159</v>
+        <v>4.5973</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3708</v>
+        <v>4.4621</v>
       </c>
       <c r="K2" t="n">
         <v>160</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>8.986699999999999</v>
+        <v>9.0594</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4229</v>
+        <v>6.4484</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7522</v>
+        <v>0.7552</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2996</v>
+        <v>2.3318</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4229</v>
+        <v>6.4484</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6578</v>
+        <v>2.6642</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7651</v>
+        <v>3.7842</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8749</v>
+        <v>3.5601</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0924</v>
+        <v>1.9989</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7651</v>
+        <v>3.7842</v>
       </c>
       <c r="K3" t="n">
         <v>160</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8575</v>
+        <v>5.783099999999999</v>
       </c>
       <c r="N3" t="n">
         <v>264</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7867</v>
+        <v>5.7497</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6777</v>
+        <v>0.6734</v>
       </c>
       <c r="D4" t="n">
-        <v>2.01</v>
+        <v>2.0135</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7867</v>
+        <v>5.7497</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1669</v>
+        <v>3.154</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6198</v>
+        <v>2.5957</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5547</v>
+        <v>5.3989</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9995</v>
+        <v>3.0313</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6198</v>
+        <v>2.5957</v>
       </c>
       <c r="K4" t="n">
         <v>94</v>
@@ -621,7 +621,7 @@
         <v>89</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6193</v>
+        <v>5.627</v>
       </c>
       <c r="N4" t="n">
         <v>183</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6609</v>
+        <v>4.7973</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5618</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4975</v>
+        <v>1.5796</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6609</v>
+        <v>4.7973</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9785</v>
+        <v>1.0969</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6824</v>
+        <v>3.7004</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9785</v>
+        <v>1.0969</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5284</v>
+        <v>0.6159</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6824</v>
+        <v>3.7004</v>
       </c>
       <c r="K5" t="n">
         <v>160</v>
@@ -667,7 +667,7 @@
         <v>104</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2108</v>
+        <v>4.3163</v>
       </c>
       <c r="N5" t="n">
         <v>264</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3076</v>
+        <v>4.4303</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5189</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3367</v>
+        <v>1.4124</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3076</v>
+        <v>4.4303</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5022</v>
+        <v>2.5724</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8054</v>
+        <v>1.8579</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3613</v>
+        <v>3.2153</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8151</v>
+        <v>1.8053</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8054</v>
+        <v>1.8579</v>
       </c>
       <c r="K6" t="n">
         <v>94</v>
@@ -713,7 +713,7 @@
         <v>89</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6205</v>
+        <v>3.6632</v>
       </c>
       <c r="N6" t="n">
         <v>183</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.639</v>
+        <v>3.5592</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4262</v>
+        <v>0.4168</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0323</v>
+        <v>1.0156</v>
       </c>
       <c r="E7" t="n">
-        <v>3.639</v>
+        <v>3.5592</v>
       </c>
       <c r="F7" t="n">
-        <v>3.639</v>
+        <v>3.5592</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2396</v>
+        <v>5.2065</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2396</v>
+        <v>5.2065</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.2396</v>
+        <v>5.2065</v>
       </c>
       <c r="N7" t="n">
         <v>149</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9115</v>
+        <v>2.9841</v>
       </c>
       <c r="C8" t="n">
-        <v>0.341</v>
+        <v>0.3495</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7012</v>
+        <v>0.7536</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9115</v>
+        <v>2.9841</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3648</v>
+        <v>2.4333</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5467</v>
+        <v>0.5508</v>
       </c>
       <c r="H8" t="n">
-        <v>2.908</v>
+        <v>2.6929</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5703</v>
+        <v>1.512</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5467</v>
+        <v>0.5508</v>
       </c>
       <c r="K8" t="n">
         <v>94</v>
@@ -805,7 +805,7 @@
         <v>89</v>
       </c>
       <c r="M8" t="n">
-        <v>2.117</v>
+        <v>2.0628</v>
       </c>
       <c r="N8" t="n">
         <v>183</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9102</v>
+        <v>2.8234</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3408</v>
+        <v>0.3307</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7006</v>
+        <v>0.6804</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9102</v>
+        <v>2.8234</v>
       </c>
       <c r="F9" t="n">
-        <v>3.164</v>
+        <v>2.8234</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2538</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5449</v>
+        <v>3.5202</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9942</v>
+        <v>3.6143</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2538</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="L9" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7404</v>
+        <v>3.6143</v>
       </c>
       <c r="N9" t="n">
-        <v>183</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9015</v>
+        <v>2.8051</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3398</v>
+        <v>0.3285</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6966</v>
+        <v>0.6721</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9015</v>
+        <v>2.8051</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9015</v>
+        <v>3.1017</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.2966</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6256</v>
+        <v>5.2024</v>
       </c>
       <c r="I10" t="n">
-        <v>3.719</v>
+        <v>2.921</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.2966</v>
       </c>
       <c r="K10" t="n">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M10" t="n">
-        <v>3.719</v>
+        <v>2.6244</v>
       </c>
       <c r="N10" t="n">
-        <v>152</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6675</v>
+        <v>2.6843</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3124</v>
+        <v>0.3144</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5901</v>
+        <v>0.617</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6675</v>
+        <v>2.6843</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5787</v>
+        <v>2.6305</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0888</v>
+        <v>0.0538</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6139</v>
+        <v>3.4335</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9515</v>
+        <v>1.9278</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0888</v>
+        <v>0.0538</v>
       </c>
       <c r="K11" t="n">
         <v>94</v>
@@ -943,7 +943,7 @@
         <v>89</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0403</v>
+        <v>1.9816</v>
       </c>
       <c r="N11" t="n">
         <v>183</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3579</v>
+        <v>2.5026</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2761</v>
+        <v>0.2931</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4492</v>
+        <v>0.5343</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3579</v>
+        <v>2.5026</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4013</v>
+        <v>-0.0265</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0434</v>
+        <v>2.5291</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0288</v>
+        <v>-0.0265</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6355</v>
+        <v>-0.0149</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0434</v>
+        <v>2.5291</v>
       </c>
       <c r="K12" t="n">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="L12" t="n">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5921</v>
+        <v>2.5142</v>
       </c>
       <c r="N12" t="n">
-        <v>121</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3218</v>
+        <v>2.3919</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2719</v>
+        <v>0.2801</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4327</v>
+        <v>0.4838</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3218</v>
+        <v>2.3919</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2822</v>
+        <v>2.469</v>
       </c>
       <c r="G13" t="n">
-        <v>2.604</v>
+        <v>-0.0771</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2822</v>
+        <v>2.8272</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1524</v>
+        <v>1.5874</v>
       </c>
       <c r="J13" t="n">
-        <v>2.604</v>
+        <v>-0.0771</v>
       </c>
       <c r="K13" t="n">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="L13" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4516</v>
+        <v>1.5103</v>
       </c>
       <c r="N13" t="n">
-        <v>264</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3108</v>
+        <v>2.3328</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2706</v>
+        <v>0.2732</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4277</v>
+        <v>0.4569</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3108</v>
+        <v>2.3328</v>
       </c>
       <c r="F14" t="n">
-        <v>2.481</v>
+        <v>2.5433</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1702</v>
+        <v>-0.2105</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2915</v>
+        <v>3.106</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7774</v>
+        <v>1.7439</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1702</v>
+        <v>-0.2105</v>
       </c>
       <c r="K14" t="n">
         <v>64</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6072</v>
+        <v>1.5334</v>
       </c>
       <c r="N14" t="n">
         <v>121</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1564</v>
+        <v>2.0423</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2525</v>
+        <v>0.2392</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3574</v>
+        <v>0.3246</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1564</v>
+        <v>2.0423</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1564</v>
+        <v>2.0423</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1564</v>
+        <v>2.0423</v>
       </c>
       <c r="I15" t="n">
-        <v>2.212</v>
+        <v>2.0969</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.212</v>
+        <v>2.0969</v>
       </c>
       <c r="N15" t="n">
         <v>152</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6293</v>
+        <v>1.7714</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1908</v>
+        <v>0.2075</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1175</v>
+        <v>0.2012</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6293</v>
+        <v>1.7714</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4178</v>
+        <v>2.546</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7885</v>
+        <v>-0.7746</v>
       </c>
       <c r="H16" t="n">
-        <v>3.083</v>
+        <v>3.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6648</v>
+        <v>1.7497</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7885</v>
+        <v>-0.7746</v>
       </c>
       <c r="K16" t="n">
         <v>85</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8763000000000001</v>
+        <v>0.9751000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>127</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3539</v>
+        <v>1.308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1586</v>
+        <v>0.1532</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3539</v>
+        <v>1.308</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3539</v>
+        <v>1.308</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3539</v>
+        <v>1.308</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3539</v>
+        <v>1.308</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3539</v>
+        <v>1.308</v>
       </c>
       <c r="N17" t="n">
         <v>149</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0003</v>
+        <v>0.8163</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1172</v>
+        <v>0.0956</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1688</v>
+        <v>-0.2339</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0003</v>
+        <v>0.8163</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1626</v>
+        <v>0.9997</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1623</v>
+        <v>-0.1834</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1626</v>
+        <v>0.9997</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6278</v>
+        <v>0.5613</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1623</v>
+        <v>-0.1834</v>
       </c>
       <c r="K18" t="n">
         <v>64</v>
@@ -1265,7 +1265,7 @@
         <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4655</v>
+        <v>0.3779</v>
       </c>
       <c r="N18" t="n">
         <v>121</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vSa</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4195</v>
+        <v>0.3989</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0491</v>
+        <v>0.0467</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4332</v>
+        <v>-0.4241</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4195</v>
+        <v>0.3989</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4195</v>
+        <v>0.3989</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4195</v>
+        <v>0.3989</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4195</v>
+        <v>0.3989</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4195</v>
+        <v>0.3989</v>
       </c>
       <c r="N19" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>vSa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3732</v>
+        <v>0.3911</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0437</v>
+        <v>0.0458</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4543</v>
+        <v>-0.4276</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3732</v>
+        <v>0.3911</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3539</v>
+        <v>0.3911</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9807</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3539</v>
+        <v>0.3911</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7311</v>
+        <v>0.3911</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9807</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="L20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2496</v>
+        <v>0.3911</v>
       </c>
       <c r="N20" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3732</v>
+        <v>0.3691</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0437</v>
+        <v>0.0432</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4543</v>
+        <v>-0.4376</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3732</v>
+        <v>0.3691</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3732</v>
+        <v>0.3691</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3732</v>
+        <v>0.3691</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3732</v>
+        <v>0.3691</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3732</v>
+        <v>0.3691</v>
       </c>
       <c r="N21" t="n">
         <v>149</v>
@@ -1412,323 +1412,323 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3712</v>
+        <v>0.211</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0435</v>
+        <v>0.0247</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4552</v>
+        <v>-0.5097</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3712</v>
+        <v>0.211</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3712</v>
+        <v>0.211</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3712</v>
+        <v>0.211</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3712</v>
+        <v>0.2166</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3712</v>
+        <v>0.2166</v>
       </c>
       <c r="N22" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2808</v>
+        <v>0.1847</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0329</v>
+        <v>0.0216</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4964</v>
+        <v>-0.5216</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2808</v>
+        <v>0.1847</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2808</v>
+        <v>1.1728</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.9881</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2808</v>
+        <v>1.1728</v>
       </c>
       <c r="I23" t="n">
-        <v>0.288</v>
+        <v>0.6585</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.9881</v>
       </c>
       <c r="K23" t="n">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M23" t="n">
-        <v>0.288</v>
+        <v>-0.3296</v>
       </c>
       <c r="N23" t="n">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1838</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0215</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5405</v>
+        <v>-0.5717</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1838</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8157</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5397</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8157</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L24" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.276</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1468</v>
+        <v>0.0684</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0172</v>
+        <v>0.008</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5574</v>
+        <v>-0.5746</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1468</v>
+        <v>0.0684</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1468</v>
+        <v>0.8709</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.8025</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1468</v>
+        <v>0.8709</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1468</v>
+        <v>0.489</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.8025</v>
       </c>
       <c r="K25" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1468</v>
+        <v>-0.3135</v>
       </c>
       <c r="N25" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0138</v>
+        <v>-0.0054</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0016</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6179</v>
+        <v>-0.6082</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0138</v>
+        <v>-0.0054</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0138</v>
+        <v>-0.0054</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0138</v>
+        <v>-0.0054</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0138</v>
+        <v>-0.0055</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0138</v>
+        <v>-0.0055</v>
       </c>
       <c r="N26" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0041</v>
+        <v>-0.0057</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0005</v>
+        <v>-0.0007</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6261</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0041</v>
+        <v>-0.0057</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0041</v>
+        <v>0.3119</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.3176</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0041</v>
+        <v>0.3119</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0042</v>
+        <v>0.1751</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.3176</v>
       </c>
       <c r="K27" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0042</v>
+        <v>-0.1425</v>
       </c>
       <c r="N27" t="n">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0474</v>
+        <v>-0.09</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0056</v>
+        <v>-0.0105</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6458</v>
+        <v>-0.6468</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0474</v>
+        <v>-0.09</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3076</v>
+        <v>-0.09</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.355</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3076</v>
+        <v>-0.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1661</v>
+        <v>-0.09</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.355</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="L28" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1889</v>
+        <v>-0.09</v>
       </c>
       <c r="N28" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.12</v>
+        <v>-0.1549</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0141</v>
+        <v>-0.0181</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6788</v>
+        <v>-0.6764</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.12</v>
+        <v>-0.1549</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7614</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9048</v>
+        <v>-0.9163</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7614</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4238</v>
+        <v>0.4275</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9048</v>
+        <v>-0.9163</v>
       </c>
       <c r="K29" t="n">
         <v>85</v>
@@ -1771,7 +1771,7 @@
         <v>42</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.481</v>
+        <v>-0.4888</v>
       </c>
       <c r="N29" t="n">
         <v>127</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1545</v>
+        <v>-0.2354</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0181</v>
+        <v>-0.0276</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6945</v>
+        <v>-0.713</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1545</v>
+        <v>-0.2354</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1545</v>
+        <v>-0.2354</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1545</v>
+        <v>-0.2354</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1545</v>
+        <v>-0.2354</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1545</v>
+        <v>-0.2354</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2012</v>
+        <v>-0.239</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0236</v>
+        <v>-0.028</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7158</v>
+        <v>-0.7147</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2012</v>
+        <v>-0.239</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2012</v>
+        <v>-0.239</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2012</v>
+        <v>-0.239</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2012</v>
+        <v>-0.239</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2012</v>
+        <v>-0.239</v>
       </c>
       <c r="N31" t="n">
         <v>91</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2343</v>
+        <v>-0.279</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0274</v>
+        <v>-0.0327</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7309</v>
+        <v>-0.7329</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2343</v>
+        <v>-0.279</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2343</v>
+        <v>-0.279</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2343</v>
+        <v>-0.279</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2403</v>
+        <v>-0.2865</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2403</v>
+        <v>-0.2865</v>
       </c>
       <c r="N32" t="n">
         <v>152</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3342</v>
+        <v>-0.368</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0391</v>
+        <v>-0.0431</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7763</v>
+        <v>-0.7734</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3342</v>
+        <v>-0.368</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3342</v>
+        <v>-0.368</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3342</v>
+        <v>-0.368</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3342</v>
+        <v>-0.368</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3342</v>
+        <v>-0.368</v>
       </c>
       <c r="N33" t="n">
         <v>77</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.495</v>
+        <v>-0.4956</v>
       </c>
       <c r="C34" t="n">
         <v>-0.058</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8495</v>
+        <v>-0.8316</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.495</v>
+        <v>-0.4956</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.495</v>
+        <v>-0.4956</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.495</v>
+        <v>-0.4956</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.495</v>
+        <v>-0.4956</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.495</v>
+        <v>-0.4956</v>
       </c>
       <c r="N34" t="n">
         <v>77</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5258</v>
+        <v>-0.5023</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0616</v>
+        <v>-0.0588</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8636</v>
+        <v>-0.8346</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5258</v>
+        <v>-0.5023</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5258</v>
+        <v>-0.5023</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5258</v>
+        <v>-0.5023</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5258</v>
+        <v>-0.5023</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5258</v>
+        <v>-0.5023</v>
       </c>
       <c r="N35" t="n">
         <v>77</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>fitch</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7532</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0882</v>
+        <v>-0.0741</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9671</v>
+        <v>-0.894</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7532</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1195</v>
+        <v>-0.8515</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3663</v>
+        <v>0.2189</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1195</v>
+        <v>-0.8515</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6045</v>
+        <v>-0.4781</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3663</v>
+        <v>0.2189</v>
       </c>
       <c r="K36" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="L36" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.2382</v>
+        <v>-0.2592</v>
       </c>
       <c r="N36" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fitch</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8457</v>
+        <v>-0.7254</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.099</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0092</v>
+        <v>-0.9362</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8457</v>
+        <v>-0.7254</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-1.0845</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1276</v>
+        <v>0.3591</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-1.0845</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5256</v>
+        <v>-0.6089</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1276</v>
+        <v>0.3591</v>
       </c>
       <c r="K37" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="L37" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.398</v>
+        <v>-0.2498</v>
       </c>
       <c r="N37" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8351</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1034</v>
+        <v>-0.0978</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.026</v>
+        <v>-0.9862</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8351</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8351</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8351</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8351</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8351</v>
       </c>
       <c r="N38" t="n">
         <v>77</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2467</v>
+        <v>-1.1998</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.146</v>
+        <v>-0.1405</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1917</v>
+        <v>-1.1524</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2467</v>
+        <v>-1.1998</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2467</v>
+        <v>-1.1998</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2467</v>
+        <v>-1.1998</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2467</v>
+        <v>-1.1998</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2467</v>
+        <v>-1.1998</v>
       </c>
       <c r="N39" t="n">
         <v>91</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3984</v>
+        <v>-1.3484</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1638</v>
+        <v>-0.1579</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2608</v>
+        <v>-1.22</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3984</v>
+        <v>-1.3484</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3984</v>
+        <v>-1.3484</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3984</v>
+        <v>-1.3484</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3984</v>
+        <v>-1.3484</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3984</v>
+        <v>-1.3484</v>
       </c>
       <c r="N40" t="n">
         <v>149</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.9121</v>
+        <v>-2.653</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3411</v>
+        <v>-0.3107</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9499</v>
+        <v>-1.8144</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.9121</v>
+        <v>-2.653</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9558</v>
+        <v>-0.7552</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.9563</v>
+        <v>-1.8978</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9558</v>
+        <v>-0.7552</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5161</v>
+        <v>-0.424</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.9563</v>
+        <v>-1.8978</v>
       </c>
       <c r="K41" t="n">
         <v>160</v>
@@ -2323,7 +2323,7 @@
         <v>104</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4724</v>
+        <v>-2.3218</v>
       </c>
       <c r="N41" t="n">
         <v>264</v>
@@ -2429,10 +2429,10 @@
         <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J2" t="n">
-        <v>36.906</v>
+        <v>39.644</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.253</v>
+        <v>1.2812</v>
       </c>
       <c r="J3" t="n">
-        <v>25.06</v>
+        <v>25.624</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.48</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0496</v>
+        <v>1.0579</v>
       </c>
       <c r="J4" t="n">
-        <v>20.992</v>
+        <v>21.158</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.39</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8875</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>17.75</v>
+        <v>17.652</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5223</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.018</v>
+        <v>-10.446</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1626</v>
+        <v>-0.1462</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.252</v>
+        <v>-2.924</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.83</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1848</v>
+        <v>-0.1689</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.696</v>
+        <v>-3.378</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.65</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3581</v>
+        <v>-0.3462</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.162</v>
+        <v>-6.924</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.52</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4725</v>
+        <v>-0.4677</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.353999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4901</v>
+        <v>-0.4871</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.802</v>
+        <v>-9.742000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.72</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4983</v>
+        <v>1.5313</v>
       </c>
       <c r="J12" t="n">
-        <v>40.4541</v>
+        <v>41.3451</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1701</v>
+        <v>1.182</v>
       </c>
       <c r="J13" t="n">
-        <v>31.5927</v>
+        <v>31.914</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.26</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6607</v>
+        <v>0.6342</v>
       </c>
       <c r="J14" t="n">
-        <v>17.8389</v>
+        <v>17.1234</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3956</v>
+        <v>0.3635</v>
       </c>
       <c r="J15" t="n">
-        <v>10.6812</v>
+        <v>9.814500000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.617</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.659</v>
+        <v>-15.8004</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2561</v>
+        <v>0.2175</v>
       </c>
       <c r="J17" t="n">
-        <v>6.9147</v>
+        <v>5.8725</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.92</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1</v>
+        <v>-0.0858</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.7</v>
+        <v>-2.3166</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3604</v>
+        <v>-0.3463</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.7308</v>
+        <v>-9.350099999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4142</v>
+        <v>-0.4039</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.1834</v>
+        <v>-10.9053</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4231</v>
+        <v>-0.4135</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.4237</v>
+        <v>-11.1645</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.83</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2033</v>
+        <v>-0.1869</v>
       </c>
       <c r="J22" t="n">
-        <v>-5.0825</v>
+        <v>-4.6725</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2033</v>
+        <v>-0.1869</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.0825</v>
+        <v>-4.6725</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2609</v>
+        <v>-0.2439</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.5225</v>
+        <v>-6.0975</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2794</v>
+        <v>-0.2625</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.985</v>
+        <v>-6.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.73</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2979</v>
+        <v>-0.2813</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.4475</v>
+        <v>-7.0325</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.76</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2784</v>
+        <v>1.2801</v>
       </c>
       <c r="J27" t="n">
-        <v>31.96</v>
+        <v>32.0025</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7754</v>
+        <v>0.7621</v>
       </c>
       <c r="J28" t="n">
-        <v>19.385</v>
+        <v>19.0525</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4593</v>
+        <v>0.4355</v>
       </c>
       <c r="J29" t="n">
-        <v>11.4825</v>
+        <v>10.8875</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.06</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1852</v>
+        <v>0.1575</v>
       </c>
       <c r="J30" t="n">
-        <v>4.63</v>
+        <v>3.9375</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.06</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1852</v>
+        <v>0.1575</v>
       </c>
       <c r="J31" t="n">
-        <v>4.63</v>
+        <v>3.9375</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3309</v>
+        <v>0.4058</v>
       </c>
       <c r="J32" t="n">
-        <v>5.6253</v>
+        <v>6.8986</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.42</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5276</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.969200000000001</v>
+        <v>-9.0219</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.41</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5363</v>
+        <v>-0.54</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.117100000000001</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.25</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6828</v>
+        <v>-0.7068</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.6076</v>
+        <v>-12.0156</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.23</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7015</v>
+        <v>-0.7294</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.9255</v>
+        <v>-12.3998</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.57</v>
       </c>
       <c r="I37" t="n">
-        <v>2.1127</v>
+        <v>2.1997</v>
       </c>
       <c r="J37" t="n">
-        <v>35.9159</v>
+        <v>37.3949</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>2.26</v>
       </c>
       <c r="I38" t="n">
-        <v>1.7807</v>
+        <v>1.8251</v>
       </c>
       <c r="J38" t="n">
-        <v>30.2719</v>
+        <v>31.0267</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6078</v>
       </c>
       <c r="J39" t="n">
-        <v>10.3768</v>
+        <v>10.3326</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.14</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3422</v>
+        <v>0.3056</v>
       </c>
       <c r="J40" t="n">
-        <v>5.8174</v>
+        <v>5.1952</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.08</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1884</v>
+        <v>0.151</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2028</v>
+        <v>2.567</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2984</v>
+        <v>0.249</v>
       </c>
       <c r="J42" t="n">
-        <v>8.056800000000001</v>
+        <v>6.723</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1702</v>
+        <v>0.1328</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5954</v>
+        <v>3.5856</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1387</v>
+        <v>-0.1216</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.7449</v>
+        <v>-3.2832</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2516</v>
+        <v>-0.2322</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.7932</v>
+        <v>-6.2694</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.436</v>
+        <v>-0.4284</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.772</v>
+        <v>-11.5668</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1563</v>
+        <v>1.1505</v>
       </c>
       <c r="J47" t="n">
-        <v>31.2201</v>
+        <v>31.0635</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.29</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6489</v>
+        <v>0.6389</v>
       </c>
       <c r="J48" t="n">
-        <v>17.5203</v>
+        <v>17.2503</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.21</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5282</v>
+        <v>0.5225</v>
       </c>
       <c r="J49" t="n">
-        <v>14.2614</v>
+        <v>14.1075</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.19</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4958</v>
+        <v>0.4836</v>
       </c>
       <c r="J50" t="n">
-        <v>13.3866</v>
+        <v>13.0572</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.96</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.216</v>
+        <v>-0.1826</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.832</v>
+        <v>-4.9302</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.34</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6179</v>
+        <v>0.5913</v>
       </c>
       <c r="J52" t="n">
-        <v>18.537</v>
+        <v>17.739</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2658</v>
+        <v>0.2179</v>
       </c>
       <c r="J53" t="n">
-        <v>7.974</v>
+        <v>6.537</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2163</v>
+        <v>-0.196</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.489</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.71</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3325</v>
+        <v>-0.3162</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.975</v>
+        <v>-9.486000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.254</v>
+        <v>-9.782999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.52</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9804</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>29.412</v>
+        <v>29.016</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.4</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8138</v>
+        <v>0.7985</v>
       </c>
       <c r="J58" t="n">
-        <v>24.414</v>
+        <v>23.955</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.28</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6387</v>
+        <v>0.6276</v>
       </c>
       <c r="J59" t="n">
-        <v>19.161</v>
+        <v>18.828</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.14</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4069</v>
+        <v>0.3734</v>
       </c>
       <c r="J60" t="n">
-        <v>12.207</v>
+        <v>11.202</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7403</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.209</v>
+        <v>-21.456</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.51</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1008</v>
+        <v>1.1127</v>
       </c>
       <c r="J62" t="n">
-        <v>27.52</v>
+        <v>27.8175</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.3</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7398</v>
+        <v>0.7164</v>
       </c>
       <c r="J63" t="n">
-        <v>18.495</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.29</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7205</v>
+        <v>0.6962</v>
       </c>
       <c r="J64" t="n">
-        <v>18.0125</v>
+        <v>17.405</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.62</v>
+        <v>0.5919</v>
       </c>
       <c r="J65" t="n">
-        <v>15.5</v>
+        <v>14.7975</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2959</v>
+        <v>0.2643</v>
       </c>
       <c r="J66" t="n">
-        <v>7.3975</v>
+        <v>6.6075</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3224</v>
+        <v>0.2755</v>
       </c>
       <c r="J67" t="n">
-        <v>8.06</v>
+        <v>6.8875</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1409</v>
+        <v>0.1107</v>
       </c>
       <c r="J68" t="n">
-        <v>3.5225</v>
+        <v>2.7675</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0362</v>
+        <v>0.0304</v>
       </c>
       <c r="J69" t="n">
-        <v>0.905</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4019</v>
+        <v>-0.3905</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.0475</v>
+        <v>-9.762499999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.32</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6596</v>
+        <v>-0.6851</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.49</v>
+        <v>-17.1275</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.95</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6252</v>
+        <v>1.6667</v>
       </c>
       <c r="J72" t="n">
-        <v>30.8788</v>
+        <v>31.6673</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.49</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0549</v>
+        <v>1.0666</v>
       </c>
       <c r="J73" t="n">
-        <v>20.0431</v>
+        <v>20.2654</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.36</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8404</v>
+        <v>0.8293</v>
       </c>
       <c r="J74" t="n">
-        <v>15.9676</v>
+        <v>15.7567</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.18</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4688</v>
+        <v>0.4387</v>
       </c>
       <c r="J75" t="n">
-        <v>8.9072</v>
+        <v>8.3353</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.15</v>
       </c>
       <c r="I76" t="n">
-        <v>0.399</v>
+        <v>0.3672</v>
       </c>
       <c r="J76" t="n">
-        <v>7.581</v>
+        <v>6.9768</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.37</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8235</v>
+        <v>0.8052</v>
       </c>
       <c r="J77" t="n">
-        <v>15.6465</v>
+        <v>15.2988</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0706</v>
+        <v>-0.0572</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.3414</v>
+        <v>-1.0868</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.52</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4826</v>
+        <v>-0.4792</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.1694</v>
+        <v>-9.104799999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5175</v>
+        <v>-0.5184</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.8325</v>
+        <v>-9.849600000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.44</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.552</v>
+        <v>-0.5579</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.488</v>
+        <v>-10.6001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.7</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3514</v>
+        <v>1.3738</v>
       </c>
       <c r="J82" t="n">
-        <v>28.3794</v>
+        <v>28.8498</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.48</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0615</v>
+        <v>1.0696</v>
       </c>
       <c r="J83" t="n">
-        <v>22.2915</v>
+        <v>22.4616</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.37</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8764</v>
+        <v>0.8603</v>
       </c>
       <c r="J84" t="n">
-        <v>18.4044</v>
+        <v>18.0663</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3104</v>
+        <v>-0.2726</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.5184</v>
+        <v>-5.7246</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.91</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3663</v>
+        <v>-0.3275</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.6923</v>
+        <v>-6.8775</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6079</v>
+        <v>0.5685</v>
       </c>
       <c r="J87" t="n">
-        <v>12.7659</v>
+        <v>11.9385</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.79</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2413</v>
+        <v>-0.2249</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.0673</v>
+        <v>-4.7229</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3782</v>
+        <v>-0.3652</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.9422</v>
+        <v>-7.6692</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3782</v>
+        <v>-0.3652</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.9422</v>
+        <v>-7.6692</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4932</v>
+        <v>-0.4911</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.3572</v>
+        <v>-10.3131</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5726</v>
       </c>
       <c r="J92" t="n">
-        <v>13.8475</v>
+        <v>14.315</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2135</v>
+        <v>0.1971</v>
       </c>
       <c r="J93" t="n">
-        <v>5.3375</v>
+        <v>4.9275</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.9</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1466</v>
+        <v>-0.127</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.665</v>
+        <v>-3.175</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.82</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.232</v>
+        <v>-0.2117</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.8</v>
+        <v>-5.2925</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2717</v>
+        <v>-0.2525</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.7925</v>
+        <v>-6.3125</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5569</v>
+        <v>0.4868</v>
       </c>
       <c r="J97" t="n">
-        <v>13.9225</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4471</v>
+        <v>0.381</v>
       </c>
       <c r="J98" t="n">
-        <v>11.1775</v>
+        <v>9.525</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3783</v>
+        <v>0.3166</v>
       </c>
       <c r="J99" t="n">
-        <v>9.4575</v>
+        <v>7.915</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0949</v>
+        <v>-0.078</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.3725</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4454</v>
+        <v>-0.4415</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.135</v>
+        <v>-11.0375</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.55</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2116</v>
+        <v>1.2315</v>
       </c>
       <c r="J102" t="n">
-        <v>33.9248</v>
+        <v>34.482</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.21</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5929</v>
+        <v>0.5541</v>
       </c>
       <c r="J103" t="n">
-        <v>16.6012</v>
+        <v>15.5148</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.95</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2114</v>
+        <v>-0.175</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.9192</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5531</v>
+        <v>-0.5129</v>
       </c>
       <c r="J105" t="n">
-        <v>-15.4868</v>
+        <v>-14.3612</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.668</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.704</v>
+        <v>-17.7408</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4987</v>
+        <v>0.4396</v>
       </c>
       <c r="J107" t="n">
-        <v>13.9636</v>
+        <v>12.3088</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.11</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2704</v>
+        <v>0.2224</v>
       </c>
       <c r="J108" t="n">
-        <v>7.5712</v>
+        <v>6.2272</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0427</v>
+        <v>0.0291</v>
       </c>
       <c r="J109" t="n">
-        <v>1.1956</v>
+        <v>0.8148</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.87</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1809</v>
+        <v>-0.1604</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.0652</v>
+        <v>-4.4912</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2432</v>
+        <v>-0.2231</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.8096</v>
+        <v>-6.2468</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.8</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2304</v>
+        <v>-0.2145</v>
       </c>
       <c r="J112" t="n">
-        <v>-5.0688</v>
+        <v>-4.719</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.79</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2402</v>
+        <v>-0.2242</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.2844</v>
+        <v>-4.9324</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2498</v>
+        <v>-0.2338</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.4956</v>
+        <v>-5.1436</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.77</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2593</v>
+        <v>-0.2432</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.7046</v>
+        <v>-5.3504</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.64</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.377</v>
+        <v>-0.364</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.294</v>
+        <v>-8.007999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4794</v>
+        <v>1.5094</v>
       </c>
       <c r="J117" t="n">
-        <v>32.5468</v>
+        <v>33.2068</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.76</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3944</v>
+        <v>1.4192</v>
       </c>
       <c r="J118" t="n">
-        <v>30.6768</v>
+        <v>31.2224</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.66</v>
       </c>
       <c r="I119" t="n">
-        <v>1.2709</v>
+        <v>1.2902</v>
       </c>
       <c r="J119" t="n">
-        <v>27.9598</v>
+        <v>28.3844</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.12</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3239</v>
+        <v>0.2912</v>
       </c>
       <c r="J120" t="n">
-        <v>7.1258</v>
+        <v>6.4064</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6141</v>
+        <v>-0.5866</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.5102</v>
+        <v>-12.9052</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5901</v>
+        <v>0.5191</v>
       </c>
       <c r="J122" t="n">
-        <v>14.1624</v>
+        <v>12.4584</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.36</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4837</v>
+        <v>0.4161</v>
       </c>
       <c r="J123" t="n">
-        <v>11.6088</v>
+        <v>9.9864</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2773</v>
+        <v>0.2263</v>
       </c>
       <c r="J124" t="n">
-        <v>6.6552</v>
+        <v>5.4312</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.11</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1876</v>
+        <v>0.1482</v>
       </c>
       <c r="J125" t="n">
-        <v>4.5024</v>
+        <v>3.5568</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3605</v>
+        <v>-0.3484</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.651999999999999</v>
+        <v>-8.361599999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.53</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7438</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>17.8512</v>
+        <v>19.2216</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1182</v>
+        <v>0.102</v>
       </c>
       <c r="J128" t="n">
-        <v>2.8368</v>
+        <v>2.448</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1997</v>
+        <v>-0.1791</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.7928</v>
+        <v>-4.2984</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2204</v>
+        <v>-0.1999</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.2896</v>
+        <v>-4.7976</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4002</v>
+        <v>-0.3898</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.604799999999999</v>
+        <v>-9.3552</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.17</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4028</v>
+        <v>0.3475</v>
       </c>
       <c r="J132" t="n">
-        <v>9.2644</v>
+        <v>7.9925</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1391</v>
+        <v>0.1056</v>
       </c>
       <c r="J133" t="n">
-        <v>3.1993</v>
+        <v>2.4288</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0557</v>
+        <v>0.0379</v>
       </c>
       <c r="J134" t="n">
-        <v>1.2811</v>
+        <v>0.8717</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1403</v>
+        <v>-0.1223</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.2269</v>
+        <v>-2.8129</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.47</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.542</v>
+        <v>-0.5486</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.466</v>
+        <v>-12.6178</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3185</v>
+        <v>1.3391</v>
       </c>
       <c r="J137" t="n">
-        <v>30.3255</v>
+        <v>30.7993</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.38</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8999</v>
+        <v>0.8845</v>
       </c>
       <c r="J138" t="n">
-        <v>20.6977</v>
+        <v>20.3435</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.24</v>
       </c>
       <c r="I139" t="n">
-        <v>0.624</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>14.352</v>
+        <v>13.6689</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.04</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1286</v>
+        <v>0.105</v>
       </c>
       <c r="J140" t="n">
-        <v>2.9578</v>
+        <v>2.415</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2771</v>
+        <v>-0.2398</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.3733</v>
+        <v>-5.5154</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9022</v>
+        <v>0.8587</v>
       </c>
       <c r="J142" t="n">
-        <v>27.066</v>
+        <v>25.761</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0007</v>
+        <v>0.0003</v>
       </c>
       <c r="J143" t="n">
-        <v>0.021</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2006</v>
+        <v>-0.18</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.018</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.83</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2213</v>
+        <v>-0.2008</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.639</v>
+        <v>-6.024</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2809</v>
+        <v>-0.262</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.427</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9925</v>
+        <v>0.9882</v>
       </c>
       <c r="J147" t="n">
-        <v>29.775</v>
+        <v>29.646</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.2</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5605</v>
+        <v>0.5219</v>
       </c>
       <c r="J148" t="n">
-        <v>16.815</v>
+        <v>15.657</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.18</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5153</v>
+        <v>0.4758</v>
       </c>
       <c r="J149" t="n">
-        <v>15.459</v>
+        <v>14.274</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.98</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1171</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.513</v>
+        <v>-2.709</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.7144</v>
       </c>
       <c r="J151" t="n">
-        <v>-22.272</v>
+        <v>-21.432</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.231</v>
+        <v>-0.2157</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.851</v>
+        <v>-4.5297</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.59</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.4017</v>
+        <v>-0.3941</v>
       </c>
       <c r="J153" t="n">
-        <v>-8.435700000000001</v>
+        <v>-8.2761</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.57</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4186</v>
+        <v>-0.4114</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.7906</v>
+        <v>-8.6394</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4271</v>
+        <v>-0.4203</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.969099999999999</v>
+        <v>-8.8263</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.49</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4883</v>
+        <v>-0.4854</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.2543</v>
+        <v>-10.1934</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.85</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4961</v>
+        <v>1.5274</v>
       </c>
       <c r="J157" t="n">
-        <v>31.4181</v>
+        <v>32.0754</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2653</v>
+        <v>1.2852</v>
       </c>
       <c r="J158" t="n">
-        <v>26.5713</v>
+        <v>26.9892</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8528</v>
+        <v>0.8445</v>
       </c>
       <c r="J159" t="n">
-        <v>17.9088</v>
+        <v>17.7345</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.26</v>
       </c>
       <c r="I160" t="n">
-        <v>0.635</v>
+        <v>0.6125</v>
       </c>
       <c r="J160" t="n">
-        <v>13.335</v>
+        <v>12.8625</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.25</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6141</v>
+        <v>0.5904</v>
       </c>
       <c r="J161" t="n">
-        <v>12.8961</v>
+        <v>12.3984</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5727</v>
+        <v>0.5191</v>
       </c>
       <c r="J162" t="n">
-        <v>16.0356</v>
+        <v>14.5348</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.85</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1907</v>
+        <v>-0.1717</v>
       </c>
       <c r="J163" t="n">
-        <v>-5.3396</v>
+        <v>-4.8076</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.77</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.27</v>
+        <v>-0.2511</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.56</v>
+        <v>-7.0308</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.27</v>
+        <v>-0.2511</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.56</v>
+        <v>-7.0308</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2986</v>
+        <v>-0.2806</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.360799999999999</v>
+        <v>-7.8568</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8082</v>
       </c>
       <c r="J167" t="n">
-        <v>23.2428</v>
+        <v>22.6296</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.34</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8082</v>
       </c>
       <c r="J168" t="n">
-        <v>23.2428</v>
+        <v>22.6296</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5224</v>
+        <v>0.4887</v>
       </c>
       <c r="J169" t="n">
-        <v>14.6272</v>
+        <v>13.6836</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.14</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4078</v>
+        <v>0.3739</v>
       </c>
       <c r="J170" t="n">
-        <v>11.4184</v>
+        <v>10.4692</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1973</v>
+        <v>0.1693</v>
       </c>
       <c r="J171" t="n">
-        <v>5.5244</v>
+        <v>4.7404</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.26</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7012</v>
+        <v>0.6677</v>
       </c>
       <c r="J172" t="n">
-        <v>41.3708</v>
+        <v>39.3943</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.18</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5231</v>
+        <v>0.4825</v>
       </c>
       <c r="J173" t="n">
-        <v>30.8629</v>
+        <v>28.4675</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.11</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3541</v>
+        <v>0.3142</v>
       </c>
       <c r="J174" t="n">
-        <v>20.8919</v>
+        <v>18.5378</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.93</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2722</v>
+        <v>-0.2321</v>
       </c>
       <c r="J175" t="n">
-        <v>-16.0598</v>
+        <v>-13.6939</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4824</v>
+        <v>-0.4401</v>
       </c>
       <c r="J176" t="n">
-        <v>-28.4616</v>
+        <v>-25.9659</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>0.982</v>
+        <v>0.9445</v>
       </c>
       <c r="J177" t="n">
-        <v>57.938</v>
+        <v>55.7255</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.14</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3155</v>
+        <v>0.2652</v>
       </c>
       <c r="J178" t="n">
-        <v>18.6145</v>
+        <v>15.6468</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1297</v>
+        <v>-0.1105</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.6523</v>
+        <v>-6.5195</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.88</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1755</v>
+        <v>-0.1551</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.3545</v>
+        <v>-9.1509</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2182</v>
+        <v>-0.1978</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.8738</v>
+        <v>-11.6702</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9473</v>
+        <v>0.9357</v>
       </c>
       <c r="J182" t="n">
-        <v>34.1028</v>
+        <v>33.6852</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.31</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8054</v>
+        <v>0.7792</v>
       </c>
       <c r="J183" t="n">
-        <v>28.9944</v>
+        <v>28.0512</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.22</v>
+        <v>0.1874</v>
       </c>
       <c r="J184" t="n">
-        <v>7.92</v>
+        <v>6.7464</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3563</v>
+        <v>-0.3136</v>
       </c>
       <c r="J185" t="n">
-        <v>-12.8268</v>
+        <v>-11.2896</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.71</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.8018</v>
+        <v>-0.7782</v>
       </c>
       <c r="J186" t="n">
-        <v>-28.8648</v>
+        <v>-28.0152</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.637</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>22.932</v>
+        <v>20.8116</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.22</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4614</v>
+        <v>0.403</v>
       </c>
       <c r="J188" t="n">
-        <v>16.6104</v>
+        <v>14.508</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1011</v>
+        <v>-0.0839</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.6396</v>
+        <v>-3.0204</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1605</v>
+        <v>-0.1403</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.778</v>
+        <v>-5.0508</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3033</v>
+        <v>-0.2857</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.9188</v>
+        <v>-10.2852</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.07</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2187</v>
+        <v>0.1762</v>
       </c>
       <c r="J192" t="n">
-        <v>5.9049</v>
+        <v>4.7574</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.04</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1491</v>
+        <v>0.1149</v>
       </c>
       <c r="J193" t="n">
-        <v>4.0257</v>
+        <v>3.1023</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.96</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0629</v>
+        <v>-0.0518</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.6983</v>
+        <v>-1.3986</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3723</v>
+        <v>-0.3587</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.0521</v>
+        <v>-9.684900000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.65</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3814</v>
+        <v>-0.3685</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.2978</v>
+        <v>-9.9495</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.48</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0681</v>
+        <v>1.0764</v>
       </c>
       <c r="J197" t="n">
-        <v>28.8387</v>
+        <v>29.0628</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.43</v>
       </c>
       <c r="I198" t="n">
-        <v>0.992</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>26.784</v>
+        <v>26.6868</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.36</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8637</v>
+        <v>0.8452</v>
       </c>
       <c r="J199" t="n">
-        <v>23.3199</v>
+        <v>22.8204</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3545</v>
+        <v>0.3217</v>
       </c>
       <c r="J200" t="n">
-        <v>9.5715</v>
+        <v>8.6859</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.82</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5859</v>
+        <v>-0.551</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.8193</v>
+        <v>-14.877</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.75</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3955</v>
+        <v>1.42</v>
       </c>
       <c r="J202" t="n">
-        <v>30.701</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.52</v>
       </c>
       <c r="I203" t="n">
-        <v>1.102</v>
+        <v>1.1155</v>
       </c>
       <c r="J203" t="n">
-        <v>24.244</v>
+        <v>24.541</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.31</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7325</v>
       </c>
       <c r="J204" t="n">
-        <v>16.533</v>
+        <v>16.115</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.19</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5004</v>
+        <v>0.4709</v>
       </c>
       <c r="J205" t="n">
-        <v>11.0088</v>
+        <v>10.3598</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.06</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1725</v>
+        <v>0.1439</v>
       </c>
       <c r="J206" t="n">
-        <v>3.795</v>
+        <v>3.1658</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3427</v>
+        <v>0.3056</v>
       </c>
       <c r="J207" t="n">
-        <v>7.5394</v>
+        <v>6.7232</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.8</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2262</v>
+        <v>-0.211</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.9764</v>
+        <v>-4.642</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.75</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2749</v>
+        <v>-0.2599</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.0478</v>
+        <v>-5.7178</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.49</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5057</v>
+        <v>-0.5049</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.1254</v>
+        <v>-11.1078</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.48</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5145</v>
+        <v>-0.5147</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.319</v>
+        <v>-11.3234</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.2</v>
       </c>
       <c r="I212" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J212" t="n">
-        <v>50.3672</v>
+        <v>51.5268</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.377</v>
+        <v>0.3443</v>
       </c>
       <c r="J213" t="n">
-        <v>9.802</v>
+        <v>8.9518</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0166</v>
+        <v>0.0065</v>
       </c>
       <c r="J214" t="n">
-        <v>0.4316</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0432</v>
+        <v>-0.038</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.1232</v>
+        <v>-0.988</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2774</v>
+        <v>-0.2402</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.2124</v>
+        <v>-6.2452</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.16</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3754</v>
+        <v>0.3204</v>
       </c>
       <c r="J217" t="n">
-        <v>9.760400000000001</v>
+        <v>8.330399999999999</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.03</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1073</v>
+        <v>0.079</v>
       </c>
       <c r="J218" t="n">
-        <v>2.7898</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0556</v>
+        <v>-0.0443</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.4456</v>
+        <v>-1.1518</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1079</v>
+        <v>-0.0912</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.8054</v>
+        <v>-2.3712</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.67</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3707</v>
+        <v>-0.3574</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.638199999999999</v>
+        <v>-9.292400000000001</v>
       </c>
     </row>
   </sheetData>
